--- a/estado_resultado/TABLERO_Resumen.xlsx
+++ b/estado_resultado/TABLERO_Resumen.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -452,7 +452,7 @@
     <col width="23" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -540,7 +540,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Febrero 2026</t>
+          <t>Enero 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -549,52 +549,52 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8950</v>
+        <v>9033</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>21750.07</v>
+        <v>21248.6</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>194663126.5</v>
+        <v>191938603.8</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>12000000</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-7331349</v>
+        <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>199331777.5</v>
+        <v>203938603.8</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.5159861109720238</v>
+        <v>0.5302666766389033</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>186704724.56</v>
+        <v>180204999.95</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>29589894.31563497</v>
+        <v>26342638.17832172</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>-16962841.37563497</v>
+        <v>-2609034.328321721</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>233134.5216142405</v>
+        <v>0</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>-17195975.89724921</v>
+        <v>-2609034.328321721</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>-0.08626811095009282</v>
+        <v>-0.01279323423671356</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Febrero 2026</t>
+          <t>Enero 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -603,13 +603,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4681</v>
+        <v>5000</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>23000</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>107663000</v>
+        <v>115000000</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -618,37 +618,37 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>21272182.42</v>
+        <v>14557254</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>128935182.42</v>
+        <v>129557254</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.3337589428979243</v>
+        <v>0.3368655724465751</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>46366452.12</v>
+        <v>62112578.1</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>19139840.46710724</v>
+        <v>16734839.80917067</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>63428889.83289278</v>
+        <v>50709836.09082934</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>150800.0502967046</v>
+        <v>0</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>63278089.78259607</v>
+        <v>50709836.09082934</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.4907744232018132</v>
+        <v>0.3914086978937462</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Febrero 2026</t>
+          <t>Enero 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>994</v>
+        <v>1005</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>18331.44</v>
+        <v>17797.52</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>18221451.36</v>
+        <v>17886507.6</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -672,37 +672,37 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>8719283.16</v>
+        <v>1879283.16</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>26940734.52</v>
+        <v>19765790.76</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.0697382274218899</v>
+        <v>0.0513936056349776</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>14154381.49</v>
+        <v>13033700.32</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>3999229.311203924</v>
+        <v>2553136.407708871</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>8787123.718796074</v>
+        <v>4178954.03229113</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>31509.35256299741</v>
+        <v>0</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>8755614.366233077</v>
+        <v>4178954.03229113</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.3249953842102252</v>
+        <v>0.2114235692886152</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Febrero 2026</t>
+          <t>Enero 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -732,31 +732,31 @@
         <v>5339979</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.01382295904566585</v>
+        <v>0.01388463422270195</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1729983.54</v>
+        <v>940255.37</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>792695.5563204675</v>
+        <v>689762.1737902485</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2817299.903679532</v>
+        <v>3709961.456209751</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>6245.534280629642</v>
+        <v>0</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>2811054.369398903</v>
+        <v>3709961.456209751</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.5264167460956125</v>
+        <v>0.6947520685399233</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Febrero 2026</t>
+          <t>Enero 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -765,13 +765,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>23006</v>
+        <v>23005.72</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>7499865</v>
+        <v>7729921.92</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
@@ -783,34 +783,34 @@
         <v>5457100.24</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>12956965.24</v>
+        <v>13187022.16</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.03354013187479501</v>
+        <v>0.03428795865644135</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>8362310.109999999</v>
+        <v>1670327.5</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>3023402.464531557</v>
+        <v>1703360.457204378</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1571252.665468444</v>
+        <v>9813334.202795623</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>15154.21138909847</v>
+        <v>0</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1556098.454079346</v>
+        <v>9813334.202795623</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0.1200974476087539</v>
+        <v>0.7441660508133721</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Febrero 2026</t>
+          <t>Enero 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -840,31 +840,31 @@
         <v>5784313.96</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.01497315532071442</v>
+        <v>0.01503996243503367</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>858655.0569682851</v>
+        <v>747156.6781320452</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>4925658.903031715</v>
+        <v>5037157.281867955</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>6765.219699759979</v>
+        <v>0</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>4918893.683331955</v>
+        <v>5037157.281867955</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.8503849751841539</v>
+        <v>0.8708305456275673</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Febrero 2026</t>
+          <t>Enero 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -894,31 +894,31 @@
         <v>7023340</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.01818047246698663</v>
+        <v>0.01826158996536719</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1042582.828233555</v>
+        <v>907200.995672081</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>5980757.171766445</v>
+        <v>6116139.004327919</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>8214.360156569415</v>
+        <v>0</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>5972542.811609875</v>
+        <v>6116139.004327919</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.8503849751841539</v>
+        <v>0.8708305456275675</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Febrero 2026</t>
+          <t>Enero 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -927,50 +927,50 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14951</v>
+        <v>15374</v>
       </c>
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="n">
-        <v>328047442.86</v>
+        <v>332555033.32</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>12000000</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-7331349</v>
+        <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>53596198.78</v>
+        <v>40041270.36</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>386312292.64</v>
+        <v>384596303.6799999</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>257317851.82</v>
+        <v>258013813.48</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>58446300</v>
+        <v>49678094.7</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>70548140.81999996</v>
+        <v>76904395.49999996</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>451823.25</v>
+        <v>0</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>70096317.56999996</v>
+        <v>76904395.49999996</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>0.1814498759306164</v>
+        <v>0.1999613484688808</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marzo 2026</t>
+          <t>Febrero 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -979,52 +979,52 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8893</v>
+        <v>8950</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>21934.95</v>
+        <v>21750.07</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>195067510.35</v>
+        <v>194663126.5</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>12000000</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-23557895.91</v>
+        <v>-7331349</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>183509614.44</v>
+        <v>199331777.5</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.5079306121308084</v>
+        <v>0.5159861109720238</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>181582548.7</v>
+        <v>216185231.65</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>31220473.13844798</v>
+        <v>29589894.31563497</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-29293407.39844803</v>
+        <v>-46443348.46563497</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0</v>
+        <v>233134.5216142405</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>-29293407.39844803</v>
+        <v>-46676482.98724921</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>-0.1596287338286886</v>
+        <v>-0.2341647858292399</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marzo 2026</t>
+          <t>Febrero 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1033,13 +1033,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4559</v>
+        <v>4681</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>23000</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>104857000</v>
+        <v>107663000</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
@@ -1048,37 +1048,37 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>20638352.53</v>
+        <v>21272182.42</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>125495352.53</v>
+        <v>128935182.42</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.3473547226648214</v>
+        <v>0.3337589428979243</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>82866813.09</v>
+        <v>53726268.12</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>21350512.31304263</v>
+        <v>19139840.46710724</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>21278027.12695737</v>
+        <v>56069073.83289278</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0</v>
+        <v>150800.0502967046</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>21278027.12695737</v>
+        <v>55918273.78259607</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.169552311683182</v>
+        <v>0.4336929047065296</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marzo 2026</t>
+          <t>Febrero 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>966</v>
+        <v>994</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>18771.39</v>
+        <v>18331.44</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>18221451.36</v>
@@ -1102,37 +1102,37 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1879283.16</v>
+        <v>8719283.16</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>20100734.52</v>
+        <v>26940734.52</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.05563620424019061</v>
+        <v>0.0697382274218899</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>6820825.960000001</v>
+        <v>13977106.66</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>3419736.039769831</v>
+        <v>3999229.311203924</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>9860172.520230168</v>
+        <v>8964398.548796074</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0</v>
+        <v>31509.35256299741</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>9860172.520230168</v>
+        <v>8932889.196233077</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.4905379209112687</v>
+        <v>0.3315755622624753</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marzo 2026</t>
+          <t>Febrero 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1156,37 +1156,37 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>6053382.07</v>
+        <v>5339979</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>6053382.07</v>
+        <v>5339979</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.01675496986716224</v>
+        <v>0.01382295904566585</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>2364242.65</v>
+        <v>1729983.54</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>1029861.312116643</v>
+        <v>792695.5563204675</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2659278.107883357</v>
+        <v>2817299.903679532</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0</v>
+        <v>6245.534280629642</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>2659278.107883357</v>
+        <v>2811054.369398903</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.4393045205361302</v>
+        <v>0.5264167460956125</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marzo 2026</t>
+          <t>Febrero 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>23005.72</v>
+        <v>23006</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>7499865</v>
@@ -1210,37 +1210,37 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>5812890.86</v>
+        <v>5457100.24</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>13312755.86</v>
+        <v>12956965.24</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.03684796708746115</v>
+        <v>0.03354013187479501</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>4725542.23</v>
+        <v>8537787.109999999</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>3364897.880114831</v>
+        <v>3023402.464531557</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>5222315.749885168</v>
+        <v>1395775.665468444</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0</v>
+        <v>15154.21138909847</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>5222315.749885168</v>
+        <v>1380621.454079346</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.3922790896794203</v>
+        <v>0.106554384341263</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marzo 2026</t>
+          <t>Febrero 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1264,37 +1264,37 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>5793567.12</v>
+        <v>5784313.96</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>5793567.12</v>
+        <v>5784313.96</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.01603583606593362</v>
+        <v>0.01497315532071442</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>985659.0195436053</v>
+        <v>858655.0569682851</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>4807908.100456395</v>
+        <v>4925658.903031715</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0</v>
+        <v>6765.219699759979</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>4807908.100456395</v>
+        <v>4918893.683331955</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>0.8298700957237543</v>
+        <v>0.8503849751841539</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marzo 2026</t>
+          <t>Febrero 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1318,37 +1318,37 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>7023340.5</v>
+        <v>7023340</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>7023340.5</v>
+        <v>7023340</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.01943968794362259</v>
+        <v>0.01818047246698663</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1194880.246964481</v>
+        <v>1042582.828233555</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>5828460.253035519</v>
+        <v>5980757.171766445</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0</v>
+        <v>8214.360156569415</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>5828460.253035519</v>
+        <v>5972542.811609875</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.8298700957237541</v>
+        <v>0.8503849751841539</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marzo 2026</t>
+          <t>Febrero 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1357,50 +1357,50 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14735</v>
+        <v>14951</v>
       </c>
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="n">
-        <v>325645826.71</v>
+        <v>328047442.86</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>12000000</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-23557895.91</v>
+        <v>-7331349</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>47200816.24</v>
+        <v>53596198.78</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>361288747.04</v>
+        <v>386312292.64</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>1</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>278359972.63</v>
+        <v>294156377.08</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>62566019.95</v>
+        <v>58446300</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>20362754.46000002</v>
+        <v>33709615.56</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0</v>
+        <v>451823.25</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>20362754.46000002</v>
+        <v>33257792.31</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.05636144116535566</v>
+        <v>0.08609043238754134</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Abril 2026</t>
+          <t>Marzo 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1409,52 +1409,52 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8981</v>
+        <v>8893</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>22121.4</v>
+        <v>21934.95</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>198672293.4</v>
+        <v>195067510.35</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>12000000</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-17601329.94</v>
+        <v>-23557895.91</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>193070963.46</v>
+        <v>183509614.44</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.5164156772140958</v>
+        <v>0.5079306121308084</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>175827647.74</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>31742016.31813437</v>
+        <v>31220473.13844798</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>161328947.1418656</v>
+        <v>-23538506.43844799</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>161328947.1418656</v>
+        <v>-23538506.43844799</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>0.8355940440276997</v>
+        <v>-0.128268518847246</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Abril 2026</t>
+          <t>Marzo 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1484,31 +1484,31 @@
         <v>125495352.53</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.3356681206878028</v>
+        <v>0.3473547226648214</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>138610187</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>20632183.40277549</v>
+        <v>21350512.31304263</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>104863169.1272245</v>
+        <v>-34465346.78304262</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>104863169.1272245</v>
+        <v>-34465346.78304262</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>0.8355940440276997</v>
+        <v>-0.2746344473179084</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Abril 2026</t>
+          <t>Marzo 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1517,13 +1517,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>959</v>
+        <v>966</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>19259.45</v>
+        <v>18771.39</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>18469812.55</v>
+        <v>18221451.36</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0</v>
@@ -1532,37 +1532,37 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>1973112</v>
+        <v>1879283.16</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>20442924.55</v>
+        <v>20100734.52</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.05467961901952231</v>
+        <v>0.05563620424019061</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>11253777.47</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>3360938.553512358</v>
+        <v>3419736.039769831</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>17081985.99648764</v>
+        <v>5427221.010230169</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>17081985.99648764</v>
+        <v>5427221.010230169</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.8355940440276997</v>
+        <v>0.2700011288060218</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Abril 2026</t>
+          <t>Marzo 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1592,31 +1592,31 @@
         <v>6053382.07</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.01619125602883504</v>
+        <v>0.01675496986716224</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>7280706.05</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>995212.0660839324</v>
+        <v>1029861.312116643</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>5058170.003916068</v>
+        <v>-2257185.292116642</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>5058170.003916068</v>
+        <v>-2257185.292116642</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0.8355940440276997</v>
+        <v>-0.3728800307026783</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Abril 2026</t>
+          <t>Marzo 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1625,13 +1625,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>24823.17</v>
+        <v>23005.72</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>7893768.06</v>
+        <v>7499865</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
@@ -1640,37 +1640,37 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>7742890.86</v>
+        <v>5812890.86</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>15636658.92</v>
+        <v>13312755.86</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.04182408198947323</v>
+        <v>0.03684796708746115</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>8720212.65</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>3670759.857955398</v>
+        <v>3364897.880114831</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>11965899.0620446</v>
+        <v>1227645.329885168</v>
       </c>
       <c r="N22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>11965899.0620446</v>
+        <v>1227645.329885168</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0.7652465352902</v>
+        <v>0.09221571722604763</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Abril 2026</t>
+          <t>Marzo 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1700,31 +1700,31 @@
         <v>5793567.12</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.01549631717863143</v>
+        <v>0.01603583606593362</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>952496.940853287</v>
+        <v>985659.0195436053</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>4841070.179146713</v>
+        <v>4807908.100456395</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>4841070.179146713</v>
+        <v>4807908.100456395</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.8355940440276995</v>
+        <v>0.8298700957237543</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Abril 2026</t>
+          <t>Marzo 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1748,37 +1748,37 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>7374506.62</v>
+        <v>7023340.5</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>7374506.62</v>
+        <v>7023340.5</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01972492788163938</v>
+        <v>0.01943968794362259</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1212412.810685158</v>
+        <v>1194880.246964481</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>6162093.809314842</v>
+        <v>5828460.253035519</v>
       </c>
       <c r="N24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>6162093.809314842</v>
+        <v>5828460.253035519</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>0.8355940440276997</v>
+        <v>0.8298700957237541</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Abril 2026</t>
+          <t>Marzo 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1787,50 +1787,50 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>14817</v>
+        <v>14735</v>
       </c>
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="n">
-        <v>329892874.01</v>
+        <v>325645826.71</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>12000000</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-17601329.94</v>
+        <v>-23557895.91</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>49575811.2</v>
+        <v>47200816.24</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>373867355.27</v>
+        <v>361288747.04</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>1</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>355219906.82</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>62566019.95</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>311301335.3200001</v>
+        <v>-56497179.72999997</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>311301335.3200001</v>
+        <v>-56497179.72999997</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>0.8326518240545073</v>
+        <v>-0.1563768044061026</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mayo 2026</t>
+          <t>Abril 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1839,52 +1839,52 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>9030</v>
+        <v>8981</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>22307.22</v>
+        <v>22121.4</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>201434196.6</v>
+        <v>198672293.4</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>12000000</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-20863268.36</v>
+        <v>-17601329.94</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>192570928.24</v>
+        <v>193070963.46</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.5239744983060236</v>
+        <v>0.5164156772140958</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>222382342.77</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1336134.97068036</v>
+        <v>31742016.31813437</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>191234793.2693197</v>
+        <v>-61053395.62813437</v>
       </c>
       <c r="N26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>191234793.2693197</v>
+        <v>-61053395.62813437</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>0.9930615956266506</v>
+        <v>-0.3162225667392149</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mayo 2026</t>
+          <t>Abril 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1893,13 +1893,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4174</v>
+        <v>4559</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>23000</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>96002000</v>
+        <v>104857000</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>0</v>
@@ -1908,37 +1908,37 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>19577254.16</v>
+        <v>20638352.53</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>115579254.16</v>
+        <v>125495352.53</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.3144845500126275</v>
+        <v>0.3356681206878028</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>110565538.2</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>801935.6025322</v>
+        <v>20632183.40277549</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>114777318.5574678</v>
+        <v>-5702369.072775494</v>
       </c>
       <c r="N27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>114777318.5574678</v>
+        <v>-5702369.072775494</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.9930615956266508</v>
+        <v>-0.04543888644332329</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mayo 2026</t>
+          <t>Abril 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1947,13 +1947,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>927</v>
+        <v>959</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>20087.6</v>
+        <v>19259.45</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>18621205.2</v>
+        <v>18469812.55</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1962,37 +1962,37 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>5733912</v>
+        <v>1973112</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>24355117.2</v>
+        <v>20442924.55</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.06626888301722196</v>
+        <v>0.05467961901952231</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>10378526.13</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>168985.651693916</v>
+        <v>3360938.553512358</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>24186131.54830608</v>
+        <v>6703459.866487642</v>
       </c>
       <c r="N28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>24186131.54830608</v>
+        <v>6703459.866487642</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.9930615956266505</v>
+        <v>0.3279110016813931</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mayo 2026</t>
+          <t>Abril 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2022,31 +2022,31 @@
         <v>6053382.07</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.01647090691295786</v>
+        <v>0.01619125602883504</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>1045103.78</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>42000.81262804255</v>
+        <v>995212.0660839324</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>6011381.257371957</v>
+        <v>4013066.223916068</v>
       </c>
       <c r="N29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>6011381.257371957</v>
+        <v>4013066.223916068</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.9930615956266506</v>
+        <v>0.6629461311891168</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mayo 2026</t>
+          <t>Abril 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2055,13 +2055,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>24823.17</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>7521420.51</v>
+        <v>7893768.06</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>0</v>
@@ -2073,34 +2073,34 @@
         <v>7742890.86</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>15264311.37</v>
+        <v>15636658.92</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.0415333195159899</v>
+        <v>0.04182408198947323</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>2703384.4</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>105909.9647657742</v>
+        <v>3670759.857955398</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>15158401.40523423</v>
+        <v>9262514.662044602</v>
       </c>
       <c r="N30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>15158401.40523423</v>
+        <v>9262514.662044602</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>0.9930615956266506</v>
+        <v>0.5923589373812729</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mayo 2026</t>
+          <t>Abril 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2124,37 +2124,37 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>6322158</v>
+        <v>5793567.12</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>6322158</v>
+        <v>5793567.12</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.01720223086910023</v>
+        <v>0.01549631717863143</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>43865.68871620558</v>
+        <v>952496.940853287</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>6278292.311283794</v>
+        <v>4841070.179146713</v>
       </c>
       <c r="N31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>6278292.311283794</v>
+        <v>4841070.179146713</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0.9930615956266506</v>
+        <v>0.8355940440276995</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Mayo 2026</t>
+          <t>Abril 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2184,31 +2184,31 @@
         <v>7374506.62</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.02006561136607911</v>
+        <v>0.01972492788163938</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>51167.30898350174</v>
+        <v>1212412.810685158</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>7323339.311016498</v>
+        <v>6162093.809314842</v>
       </c>
       <c r="N32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>7323339.311016498</v>
+        <v>6162093.809314842</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0.9930615956266506</v>
+        <v>0.8355940440276997</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mayo 2026</t>
+          <t>Abril 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2217,44 +2217,474 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>14434</v>
+        <v>14817</v>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="n">
-        <v>323578822.31</v>
+        <v>329892874.01</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>12000000</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>-20863268.36</v>
+        <v>-17601329.94</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>52804103.71</v>
+        <v>49575811.2</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>367519657.66</v>
+        <v>373867355.27</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>1</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>347074895.28</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>2550000</v>
+        <v>62566019.95</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>364969657.66</v>
+        <v>-35773559.95999993</v>
       </c>
       <c r="N33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>364969657.66</v>
+        <v>-35773559.95999993</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>0.9930615956266506</v>
+        <v>-0.0956851660240968</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Mayo 2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>OSPEVIC</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>9030</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>22307.22</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>201434196.6</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>-20863268.36</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>192570928.24</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>0.5239744982062241</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>17450261.20128772</v>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>175120667.0387123</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>175120667.0387123</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>0.9093826811722091</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Mayo 2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>OSPIF</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>4174</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>23000</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>96002000</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>19577254.23</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>115579254.23</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>0.3144845501431949</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>10473482.13043821</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>105105772.0995618</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>105105772.0995618</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>0.9093826811722091</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Mayo 2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>OSPLYFC</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>927</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>20087.6</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>18621205.2</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>5733912</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>24355117.2</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>0.06626888300459997</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>2206995.420400614</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>22148121.77959938</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>22148121.77959938</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>0.909382681172209</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Mayo 2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>OSPM</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>6053382.07</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>6053382.07</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>0.01647090690982071</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>548541.2530236229</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>5504840.816976378</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>5504840.816976378</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>0.9093826811722091</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Mayo 2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>OSSURRBAC</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>303</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>24823.17</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>7521420.51</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>7742890.86</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>15264311.37</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>0.0415333195080792</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>1383210.970101964</v>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>13881100.39989804</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>13881100.39989804</v>
+      </c>
+      <c r="P38" s="3" t="n">
+        <v>0.9093826811722091</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Mayo 2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>AMSURRBAC</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>6322158</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>6322158</v>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>0.01720223086582379</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>572897.0071656689</v>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>5749260.992834331</v>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="2" t="n">
+        <v>5749260.992834331</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>0.9093826811722091</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Mayo 2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>UOM</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>7374506.62</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>7374506.62</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>0.02006561136225729</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>668258.0175821946</v>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>6706248.602417805</v>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="2" t="n">
+        <v>6706248.602417805</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>0.9093826811722091</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Mayo 2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>14434</v>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="n">
+        <v>323578822.31</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>-20863268.36</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>52804103.78</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>367519657.73</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>33303646</v>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>334216011.73</v>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v>334216011.73</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>0.9093826811722091</v>
       </c>
     </row>
   </sheetData>
@@ -68256,7 +68686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -68296,11 +68726,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Febrero 2026</t>
+          <t>Enero 2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>451823.25</v>
+        <v>0</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>0</v>
@@ -68309,17 +68739,17 @@
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>451823.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marzo 2026</t>
+          <t>Febrero 2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0</v>
+        <v>451823.25</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>0</v>
@@ -68328,13 +68758,13 @@
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>451823.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abril 2026</t>
+          <t>Marzo 2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -68353,19 +68783,38 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Abril 2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Mayo 2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2" t="n">
+      <c r="B6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="n">
         <v>0</v>
       </c>
     </row>

--- a/estado_resultado/TABLERO_Resumen.xlsx
+++ b/estado_resultado/TABLERO_Resumen.xlsx
@@ -1433,22 +1433,22 @@
         <v>0.5079306121308084</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>168990842.89</v>
+        <v>175058830.74</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>31220473.13844798</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-16701701.58844797</v>
+        <v>-22769689.43844799</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>-16701701.58844797</v>
+        <v>-22769689.43844799</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>-0.09101267876026588</v>
+        <v>-0.1240789999365005</v>
       </c>
     </row>
     <row r="19">
@@ -1487,22 +1487,22 @@
         <v>0.3473547226648214</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>138146920</v>
+        <v>138289692.02</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>21350512.31304263</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>-34002079.78304262</v>
+        <v>-34144851.80304264</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>-34002079.78304262</v>
+        <v>-34144851.80304264</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>-0.2709429400974377</v>
+        <v>-0.2720806078845049</v>
       </c>
     </row>
     <row r="20">
@@ -1541,22 +1541,22 @@
         <v>0.05563620424019061</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>7946965.56</v>
+        <v>11698236.07</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>3419736.039769831</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>8734032.920230171</v>
+        <v>4982762.410230169</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>8734032.920230171</v>
+        <v>4982762.410230169</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.4345131224702216</v>
+        <v>0.2478895686758301</v>
       </c>
     </row>
     <row r="21">
@@ -1649,22 +1649,22 @@
         <v>0.03684796708746115</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>3676367.4</v>
+        <v>4690156.07</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>3364897.880114831</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>6271490.579885168</v>
+        <v>5257701.909885168</v>
       </c>
       <c r="N22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>6271490.579885168</v>
+        <v>5257701.909885168</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0.4710888298288953</v>
+        <v>0.3949371538978383</v>
       </c>
     </row>
     <row r="23">
@@ -1809,22 +1809,22 @@
         <v>1</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>339569177.81</v>
+        <v>343269544.13</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>62566019.95</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-40846450.71999998</v>
+        <v>-44546817.03999998</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>-40846450.71999998</v>
+        <v>-44546817.03999998</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>-0.1130576334155176</v>
+        <v>-0.1232997634301297</v>
       </c>
     </row>
     <row r="26">
@@ -1863,22 +1863,22 @@
         <v>0.5164156772140958</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>182824948.28</v>
+        <v>220822555.04</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>31742016.31813437</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-21496001.13813436</v>
+        <v>-59493607.89813435</v>
       </c>
       <c r="N26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>-21496001.13813436</v>
+        <v>-59493607.89813435</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-0.1113373070341976</v>
+        <v>-0.3081437355051067</v>
       </c>
     </row>
     <row r="27">
@@ -1917,22 +1917,22 @@
         <v>0.3356681206878028</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>109191290.09</v>
+        <v>106763986.2</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>20632183.40277549</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>-4328120.962775495</v>
+        <v>-1900817.072775494</v>
       </c>
       <c r="N27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>-4328120.962775495</v>
+        <v>-1900817.072775494</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.03448829678167441</v>
+        <v>-0.01514651367126204</v>
       </c>
     </row>
     <row r="28">
@@ -1971,22 +1971,22 @@
         <v>0.05467961901952231</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>13720138.34</v>
+        <v>8942130.01</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>3360938.553512358</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>3361847.656487643</v>
+        <v>8139855.986487643</v>
       </c>
       <c r="N28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>3361847.656487643</v>
+        <v>8139855.986487643</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.1644504262716971</v>
+        <v>0.3981747311437219</v>
       </c>
     </row>
     <row r="29">
@@ -2025,22 +2025,22 @@
         <v>0.01619125602883504</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>22093786.28</v>
+        <v>1045103.78</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>995212.0660839324</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>-17035616.27608394</v>
+        <v>4013066.223916068</v>
       </c>
       <c r="N29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>-17035616.27608394</v>
+        <v>4013066.223916068</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-2.814231132132047</v>
+        <v>0.6629461311891168</v>
       </c>
     </row>
     <row r="30">
@@ -2079,22 +2079,22 @@
         <v>0.04182408198947323</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>6362292.28</v>
+        <v>2466796.4</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>3670759.857955398</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>5603606.782044603</v>
+        <v>9499102.662044602</v>
       </c>
       <c r="N30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>5603606.782044603</v>
+        <v>9499102.662044602</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>0.3583634336921767</v>
+        <v>0.6074892795605342</v>
       </c>
     </row>
     <row r="31">
@@ -2239,22 +2239,22 @@
         <v>1</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>334192455.27</v>
+        <v>340040571.43</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>62566019.95</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>-22891119.94999994</v>
+        <v>-28739236.10999997</v>
       </c>
       <c r="N33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>-22891119.94999994</v>
+        <v>-28739236.10999997</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>-0.06122791847784732</v>
+        <v>-0.07687014045193924</v>
       </c>
     </row>
     <row r="34">
@@ -3083,13 +3083,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>167964383.22</v>
+        <v>172178119.42</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>152577623.9</v>
+        <v>156694237</v>
       </c>
     </row>
     <row r="19">
@@ -3104,13 +3104,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>117676579.76</v>
+        <v>121580968.88</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>110504630.57</v>
+        <v>113888648</v>
       </c>
     </row>
     <row r="20">
@@ -3184,17 +3184,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sin Clasificacion</t>
+          <t>Traslado</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>9885849.32</v>
+        <v>6138973.74</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>9043176.73</v>
+        <v>6138973.74</v>
       </c>
     </row>
     <row r="24">
@@ -3205,17 +3205,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Traslado</t>
+          <t>Intereses</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>6138973.74</v>
+        <v>3475904.52</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>6138973.74</v>
+        <v>3475904.52</v>
       </c>
     </row>
     <row r="25">
@@ -3226,17 +3226,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Protesis</t>
+          <t>Sin Clasificacion</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>1550000</v>
+        <v>1767724</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1550000</v>
+        <v>1767724</v>
       </c>
     </row>
     <row r="26">
@@ -3247,17 +3247,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Intereses</t>
+          <t>Protesis</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>3475904.52</v>
+        <v>1550000</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>716</v>
+        <v>1550000</v>
       </c>
     </row>
     <row r="27">
@@ -3278,7 +3278,7 @@
         <v>180930288.7</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>139978334.49</v>
+        <v>180930288.7</v>
       </c>
     </row>
     <row r="28">
@@ -3299,7 +3299,7 @@
         <v>94841189</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>127785122.09</v>
+        <v>94463303.86</v>
       </c>
     </row>
     <row r="29">
@@ -3320,7 +3320,7 @@
         <v>21983134.71</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>35776264.2</v>
+        <v>21800969.87</v>
       </c>
     </row>
     <row r="30">
@@ -3331,17 +3331,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Refacturacion</t>
+          <t>Capitado</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>12270909.17</v>
+        <v>17408543.33</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>11129136.43</v>
+        <v>17408543.33</v>
       </c>
     </row>
     <row r="31">
@@ -3352,17 +3352,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capitado</t>
+          <t>Refacturacion</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>17408543.33</v>
+        <v>12270909.17</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>10052204.05</v>
+        <v>12270909.17</v>
       </c>
     </row>
     <row r="32">
@@ -3383,7 +3383,7 @@
         <v>7111354.93</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>7085638.46</v>
+        <v>7111354.93</v>
       </c>
     </row>
     <row r="33">
@@ -3404,7 +3404,7 @@
         <v>6055201.57</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>2385755.55</v>
+        <v>6055201.57</v>
       </c>
     </row>
   </sheetData>
@@ -3429,7 +3429,7 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="43" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10347,30 +10347,30 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA INTEGRAL DE PSIQUIATRIA SAN NICOLA</t>
+          <t>SOCIEDAD DE BENEFICENCIA HOSPITAL ITALIANO</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D198" s="2" t="n">
-        <v>12666500</v>
+        <v>12879744.9</v>
       </c>
       <c r="E198" s="2" t="n">
-        <v>106800</v>
+        <v>0</v>
       </c>
       <c r="F198" s="2" t="n">
-        <v>336000</v>
+        <v>530839.21</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>0.035</v>
+        <v>0.0412</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>12223700</v>
+        <v>12348905.69</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPLYFC, OSPM, OSSURRBAC</t>
+          <t>OSPEVIC, OSPIF</t>
         </is>
       </c>
     </row>
@@ -10382,30 +10382,30 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE BENEFICENCIA HOSPITAL ITALIANO</t>
+          <t>CLINICA PRIVADA INTEGRAL DE PSIQUIATRIA SAN NICOLA</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D199" s="2" t="n">
-        <v>12879744.9</v>
+        <v>12666500</v>
       </c>
       <c r="E199" s="2" t="n">
-        <v>0</v>
+        <v>106800</v>
       </c>
       <c r="F199" s="2" t="n">
-        <v>530839.21</v>
+        <v>336000</v>
       </c>
       <c r="G199" s="3" t="n">
-        <v>0.0412</v>
+        <v>0.035</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>11664579.91</v>
+        <v>12223700</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPIF</t>
+          <t>OSPEVIC, OSPLYFC, OSPM, OSSURRBAC</t>
         </is>
       </c>
     </row>
@@ -10452,30 +10452,30 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>CLINICA CHUTRO S R L</t>
+          <t>INSTITUTO CONCI CARPINELLA SRL</t>
         </is>
       </c>
       <c r="C201" t="n">
         <v>25</v>
       </c>
       <c r="D201" s="2" t="n">
-        <v>11760871.87</v>
+        <v>10756193.7</v>
       </c>
       <c r="E201" s="2" t="n">
-        <v>351607.37</v>
+        <v>44380</v>
       </c>
       <c r="F201" s="2" t="n">
-        <v>178214.65</v>
+        <v>0</v>
       </c>
       <c r="G201" s="3" t="n">
-        <v>0.045</v>
+        <v>0.004099999999999999</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>10388377.26</v>
+        <v>10711813.7</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>GENERAL, OSPEVIC, OSPIF, OSPLYFC, OSSURRBAC</t>
+          <t>OSPEVIC, OSPIF, OSPLYFC, OSSURRBAC</t>
         </is>
       </c>
     </row>
@@ -10487,30 +10487,30 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>CAMARA DE ENTIDADES DE SALUD - CES</t>
+          <t>CLINICA CHUTRO S R L</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D202" s="2" t="n">
-        <v>11325136.14</v>
+        <v>11760871.87</v>
       </c>
       <c r="E202" s="2" t="n">
-        <v>713263</v>
+        <v>591369.46</v>
       </c>
       <c r="F202" s="2" t="n">
-        <v>439078.5</v>
+        <v>555947.35</v>
       </c>
       <c r="G202" s="3" t="n">
-        <v>0.1018</v>
+        <v>0.09759999999999999</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>10172794.64</v>
+        <v>10613555.06</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPIF, OSPLYFC, OSPM</t>
+          <t>OSPEVIC, OSPIF, OSPLYFC, OSSURRBAC</t>
         </is>
       </c>
     </row>
@@ -10522,30 +10522,30 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>INSTITUTO CONCI CARPINELLA SRL</t>
+          <t>CAMARA DE ENTIDADES DE SALUD - CES</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D203" s="2" t="n">
-        <v>10756193.7</v>
+        <v>11325136.14</v>
       </c>
       <c r="E203" s="2" t="n">
-        <v>44380</v>
+        <v>713263</v>
       </c>
       <c r="F203" s="2" t="n">
-        <v>0</v>
+        <v>439078.5</v>
       </c>
       <c r="G203" s="3" t="n">
-        <v>0.004099999999999999</v>
+        <v>0.1018</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>9257938.789999999</v>
+        <v>10172794.64</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPIF, OSPLYFC, OSSURRBAC</t>
+          <t>OSPEVIC, OSPIF, OSPLYFC, OSPM</t>
         </is>
       </c>
     </row>
@@ -10576,7 +10576,7 @@
         <v>0.0062</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>7128334.12</v>
+        <v>7777696.06</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
@@ -10697,30 +10697,30 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>CARRILLO ROMAN MARCEL</t>
+          <t>SANATORIO DEL SALVADOR PRIVADO SA</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D208" s="2" t="n">
-        <v>5048410.59</v>
+        <v>5200718.97</v>
       </c>
       <c r="E208" s="2" t="n">
-        <v>73445.45</v>
+        <v>76915.75999999999</v>
       </c>
       <c r="F208" s="2" t="n">
-        <v>0</v>
+        <v>83025.64</v>
       </c>
       <c r="G208" s="3" t="n">
-        <v>0.0145</v>
+        <v>0.0308</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>4974965.14</v>
+        <v>5040777.57</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPEVIC, OSPIF, OSPM</t>
         </is>
       </c>
     </row>
@@ -10732,30 +10732,30 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ASOCIACION DE CLINICAS DEL NORTE DE LA PROVINCIA D</t>
+          <t>CARRILLO ROMAN MARCEL</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D209" s="2" t="n">
-        <v>5077070.28</v>
+        <v>5048410.59</v>
       </c>
       <c r="E209" s="2" t="n">
-        <v>236300.04</v>
+        <v>73445.45</v>
       </c>
       <c r="F209" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G209" s="3" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.0145</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>4840770.24</v>
+        <v>4974965.14</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPIF, OSPLYFC</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
     </row>
@@ -10767,30 +10767,30 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>INSTITUTO PRIVADO DE RADIOTERAPIA S A</t>
+          <t>ASOCIACION DE CLINICAS DEL NORTE DE LA PROVINCIA D</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D210" s="2" t="n">
-        <v>4542300</v>
+        <v>5077070.28</v>
       </c>
       <c r="E210" s="2" t="n">
-        <v>0</v>
+        <v>236300.04</v>
       </c>
       <c r="F210" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G210" s="3" t="n">
-        <v>0</v>
+        <v>0.04650000000000001</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>4542300</v>
+        <v>4840770.24</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC, OSPIF, OSPLYFC</t>
         </is>
       </c>
     </row>
@@ -10802,30 +10802,30 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>SANATORIO DEL SALVADOR PRIVADO SA</t>
+          <t>INSTITUTO PRIVADO DE RADIOTERAPIA S A</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D211" s="2" t="n">
-        <v>5200718.97</v>
+        <v>4542300</v>
       </c>
       <c r="E211" s="2" t="n">
-        <v>76915.75999999999</v>
+        <v>0</v>
       </c>
       <c r="F211" s="2" t="n">
-        <v>83025.64</v>
+        <v>0</v>
       </c>
       <c r="G211" s="3" t="n">
-        <v>0.0308</v>
+        <v>0</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>4468984.46</v>
+        <v>4542300</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPIF, OSPM</t>
+          <t>OSPIF</t>
         </is>
       </c>
     </row>
@@ -10856,7 +10856,7 @@
         <v>0.2163</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>3022654.06</v>
+        <v>3138486.84</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
@@ -13987,14 +13987,14 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>CAMARA DE ENTIDADES DE SALUD - CES</t>
+          <t>SOCIEDAD DE BENEFICENCIA HOSPITAL ITALIANO</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D302" s="2" t="n">
-        <v>32727873.42</v>
+        <v>39912552.99</v>
       </c>
       <c r="E302" s="2" t="n">
         <v>0</v>
@@ -14006,7 +14006,7 @@
         <v>0</v>
       </c>
       <c r="H302" s="2" t="n">
-        <v>32727873.42</v>
+        <v>39912552.99</v>
       </c>
       <c r="I302" t="inlineStr">
         <is>
@@ -14022,14 +14022,14 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>ASOCIACION PRESTADORES DE HEMODIALISIS Y TRANSPLAN</t>
+          <t>SERVICIOS MEDICOS S R L</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D303" s="2" t="n">
-        <v>26000000</v>
+        <v>35335780.06</v>
       </c>
       <c r="E303" s="2" t="n">
         <v>0</v>
@@ -14041,7 +14041,7 @@
         <v>0</v>
       </c>
       <c r="H303" s="2" t="n">
-        <v>26000000</v>
+        <v>35335780.06</v>
       </c>
       <c r="I303" t="inlineStr">
         <is>
@@ -14057,14 +14057,14 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>SERVICIOS MEDICOS S R L</t>
+          <t>CAMARA DE ENTIDADES DE SALUD - CES</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D304" s="2" t="n">
-        <v>35335780.06</v>
+        <v>32727873.42</v>
       </c>
       <c r="E304" s="2" t="n">
         <v>0</v>
@@ -14076,7 +14076,7 @@
         <v>0</v>
       </c>
       <c r="H304" s="2" t="n">
-        <v>23701403.55</v>
+        <v>32727873.42</v>
       </c>
       <c r="I304" t="inlineStr">
         <is>
@@ -14092,14 +14092,14 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>SANATORIO MORRA S A</t>
+          <t>ASOCIACION PRESTADORES DE HEMODIALISIS Y TRANSPLAN</t>
         </is>
       </c>
       <c r="C305" t="n">
         <v>2</v>
       </c>
       <c r="D305" s="2" t="n">
-        <v>469707.97</v>
+        <v>26000000</v>
       </c>
       <c r="E305" s="2" t="n">
         <v>0</v>
@@ -14111,11 +14111,11 @@
         <v>0</v>
       </c>
       <c r="H305" s="2" t="n">
-        <v>23622048.16</v>
+        <v>26000000</v>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>OSPIF, OSPM</t>
+          <t>OSPEVIC, OSPIF</t>
         </is>
       </c>
     </row>
@@ -14127,14 +14127,14 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE BENEFICENCIA HOSPITAL ITALIANO</t>
+          <t>SAN FRANCISCO SALUD-CONSORCIO DE COOPERACION</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D306" s="2" t="n">
-        <v>39912552.99</v>
+        <v>13685686.47</v>
       </c>
       <c r="E306" s="2" t="n">
         <v>0</v>
@@ -14146,11 +14146,11 @@
         <v>0</v>
       </c>
       <c r="H306" s="2" t="n">
-        <v>23251080.7</v>
+        <v>13685686.47</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPIF</t>
+          <t>OSPEVIC, OSPIF, OSPM</t>
         </is>
       </c>
     </row>
@@ -14162,14 +14162,14 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA DEL SOL S.A.</t>
+          <t>ECCO S. A. U.</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D307" s="2" t="n">
-        <v>6514261.7</v>
+        <v>11465321.32</v>
       </c>
       <c r="E307" s="2" t="n">
         <v>0</v>
@@ -14181,11 +14181,11 @@
         <v>0</v>
       </c>
       <c r="H307" s="2" t="n">
-        <v>10667522.8</v>
+        <v>11465321.32</v>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPLYFC</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
     </row>
@@ -14232,14 +14232,14 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>ASOCIACION DE CLINICAS DEL NORTE DE LA PROVINCIA D</t>
+          <t>CLINICA PRIVADA CARAFFA SRL</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D309" s="2" t="n">
-        <v>9692243.75</v>
+        <v>9755631.640000001</v>
       </c>
       <c r="E309" s="2" t="n">
         <v>0</v>
@@ -14251,11 +14251,11 @@
         <v>0</v>
       </c>
       <c r="H309" s="2" t="n">
-        <v>9692243.75</v>
+        <v>9755631.640000001</v>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPIF, OSPLYFC</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
     </row>
@@ -14267,14 +14267,14 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>CLINICA CHUTRO S R L</t>
+          <t>ASOCIACION DE CLINICAS DEL NORTE DE LA PROVINCIA D</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D310" s="2" t="n">
-        <v>553173.98</v>
+        <v>9692243.75</v>
       </c>
       <c r="E310" s="2" t="n">
         <v>0</v>
@@ -14286,11 +14286,11 @@
         <v>0</v>
       </c>
       <c r="H310" s="2" t="n">
-        <v>9029951.640000001</v>
+        <v>9692243.75</v>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>OSPIF, OSSURRBAC</t>
+          <t>OSPEVIC, OSPIF, OSPLYFC</t>
         </is>
       </c>
     </row>
@@ -14302,14 +14302,14 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>SALOMON MARIO RAMIRO</t>
+          <t>CLINICA PRIVADA INTEGRAL DE PSIQUIATRIA SAN NICOLA</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D311" s="2" t="n">
-        <v>1771000</v>
+        <v>6563200</v>
       </c>
       <c r="E311" s="2" t="n">
         <v>0</v>
@@ -14321,11 +14321,11 @@
         <v>0</v>
       </c>
       <c r="H311" s="2" t="n">
-        <v>7800446.33</v>
+        <v>6563200</v>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPEVIC, OSPIF, OSPLYFC</t>
         </is>
       </c>
     </row>
@@ -14337,14 +14337,14 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>AMPARAR S.R.L</t>
+          <t>CLINICA PRIVADA DEL SOL S.A.</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D312" s="2" t="n">
-        <v>6073263.86</v>
+        <v>6514261.7</v>
       </c>
       <c r="E312" s="2" t="n">
         <v>0</v>
@@ -14356,11 +14356,11 @@
         <v>0</v>
       </c>
       <c r="H312" s="2" t="n">
-        <v>6073263.86</v>
+        <v>6514261.7</v>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPIF, OSPLYFC, OSSURRBAC</t>
+          <t>OSPEVIC, OSPLYFC</t>
         </is>
       </c>
     </row>
@@ -14372,30 +14372,30 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>CARRILLO ROMAN MARCEL</t>
+          <t>AMPARAR S.R.L</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D313" s="2" t="n">
-        <v>5834277.2</v>
+        <v>6073263.86</v>
       </c>
       <c r="E313" s="2" t="n">
-        <v>122064.84</v>
+        <v>0</v>
       </c>
       <c r="F313" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G313" s="3" t="n">
-        <v>0.0209</v>
+        <v>0</v>
       </c>
       <c r="H313" s="2" t="n">
-        <v>5712212.36</v>
+        <v>6073263.86</v>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPEVIC, OSPIF, OSPLYFC, OSSURRBAC</t>
         </is>
       </c>
     </row>
@@ -14407,14 +14407,14 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>SANATORIO PARQUE S A</t>
+          <t>SOP S R L</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D314" s="2" t="n">
-        <v>677538.41</v>
+        <v>5940972</v>
       </c>
       <c r="E314" s="2" t="n">
         <v>0</v>
@@ -14426,11 +14426,11 @@
         <v>0</v>
       </c>
       <c r="H314" s="2" t="n">
-        <v>5457974.59</v>
+        <v>5940972</v>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPEVIC, OSPIF</t>
         </is>
       </c>
     </row>
@@ -14442,30 +14442,30 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>SALUD INTEGRAL SOCIEDAD ANONIMA</t>
+          <t>CARRILLO ROMAN MARCEL</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D315" s="2" t="n">
-        <v>915313</v>
+        <v>5834277.2</v>
       </c>
       <c r="E315" s="2" t="n">
-        <v>3372</v>
+        <v>122064.84</v>
       </c>
       <c r="F315" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G315" s="3" t="n">
-        <v>0.0037</v>
+        <v>0.0209</v>
       </c>
       <c r="H315" s="2" t="n">
-        <v>5338261.34</v>
+        <v>5712212.36</v>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPLYFC, OSSURRBAC</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
     </row>
@@ -14477,30 +14477,30 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>ECCO S. A. U.</t>
+          <t>CIRCULO MEDICO REGIONAL RIO TERCERO</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D316" s="2" t="n">
-        <v>11465321.32</v>
+        <v>4645450.64</v>
       </c>
       <c r="E316" s="2" t="n">
-        <v>0</v>
+        <v>12892.04</v>
       </c>
       <c r="F316" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G316" s="3" t="n">
-        <v>0</v>
+        <v>0.0028</v>
       </c>
       <c r="H316" s="2" t="n">
-        <v>5148862.02</v>
+        <v>4632558.6</v>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPEVIC, OSPLYFC, OSPM</t>
         </is>
       </c>
     </row>
@@ -14512,14 +14512,14 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>DIAGNOSTICO Y TRATAMIENTO EN SALUD AMBULATORIA DEL</t>
+          <t>INSTITUTO CONCI CARPINELLA SRL</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D317" s="2" t="n">
-        <v>39467</v>
+        <v>4389460.24</v>
       </c>
       <c r="E317" s="2" t="n">
         <v>0</v>
@@ -14531,11 +14531,11 @@
         <v>0</v>
       </c>
       <c r="H317" s="2" t="n">
-        <v>4392027.4</v>
+        <v>4389460.24</v>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPEVIC, OSPIF, OSPLYFC, OSSURRBAC</t>
         </is>
       </c>
     </row>
@@ -14566,7 +14566,7 @@
         <v>0</v>
       </c>
       <c r="H318" s="2" t="n">
-        <v>4171816.14</v>
+        <v>4080214.18</v>
       </c>
       <c r="I318" t="inlineStr">
         <is>
@@ -14582,14 +14582,14 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>INSTITUTO CONCI CARPINELLA SRL</t>
+          <t>PROYECTOS INNOVADORES S R L</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D319" s="2" t="n">
-        <v>4389460.24</v>
+        <v>3630000</v>
       </c>
       <c r="E319" s="2" t="n">
         <v>0</v>
@@ -14601,11 +14601,11 @@
         <v>0</v>
       </c>
       <c r="H319" s="2" t="n">
-        <v>4028937.18</v>
+        <v>3630000</v>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPIF, OSPLYFC, OSSURRBAC</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
     </row>
@@ -14617,30 +14617,30 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA DE LA CIUDAD SOC RESP LTDA</t>
+          <t>SANATORIO DEL SALVADOR PRIVADO SA</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D320" s="2" t="n">
-        <v>159125.42</v>
+        <v>3269563.53</v>
       </c>
       <c r="E320" s="2" t="n">
-        <v>0</v>
+        <v>20519.13</v>
       </c>
       <c r="F320" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G320" s="3" t="n">
-        <v>0</v>
+        <v>0.0063</v>
       </c>
       <c r="H320" s="2" t="n">
-        <v>3943224.26</v>
+        <v>3249044.4</v>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPIF, OSPLYFC, OSSURRBAC</t>
+          <t>OSPEVIC, OSPIF, OSPM</t>
         </is>
       </c>
     </row>
@@ -14652,30 +14652,30 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>POLICLINICO PRIVADO SAN LUCAS S A</t>
+          <t>CLINICA PRIVADA DEAN FUNES S.R.L.</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D321" s="2" t="n">
-        <v>2208364.31</v>
+        <v>2850705.51</v>
       </c>
       <c r="E321" s="2" t="n">
-        <v>10531.67</v>
+        <v>0</v>
       </c>
       <c r="F321" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G321" s="3" t="n">
-        <v>0.0048</v>
+        <v>0</v>
       </c>
       <c r="H321" s="2" t="n">
-        <v>3931884.33</v>
+        <v>2850705.51</v>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPLYFC</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
     </row>
@@ -14687,14 +14687,14 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>SANCHEZ LUIS FERNANDO</t>
+          <t>FEDERACION DE BIOQUIMICOS DE LA PROVINCIA DE CORDO</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D322" s="2" t="n">
-        <v>260000</v>
+        <v>2565889.5</v>
       </c>
       <c r="E322" s="2" t="n">
         <v>0</v>
@@ -14706,11 +14706,11 @@
         <v>0</v>
       </c>
       <c r="H322" s="2" t="n">
-        <v>3889601.55</v>
+        <v>2565889.5</v>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPEVIC, OSPIF</t>
         </is>
       </c>
     </row>
@@ -14722,30 +14722,30 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>DELFINO IRINA MARIEL</t>
+          <t>POLICLINICO PRIVADO SAN LUCAS S A</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D323" s="2" t="n">
-        <v>204000</v>
+        <v>2208364.31</v>
       </c>
       <c r="E323" s="2" t="n">
-        <v>0</v>
+        <v>10531.67</v>
       </c>
       <c r="F323" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G323" s="3" t="n">
-        <v>0</v>
+        <v>0.0048</v>
       </c>
       <c r="H323" s="2" t="n">
-        <v>3076639.9</v>
+        <v>2197832.64</v>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPEVIC, OSPLYFC</t>
         </is>
       </c>
     </row>
@@ -14757,30 +14757,30 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>RESONANCIA MAGNETICA SRL</t>
+          <t>ARNODO DANIEL</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D324" s="2" t="n">
-        <v>1635936.24</v>
+        <v>2143488.45</v>
       </c>
       <c r="E324" s="2" t="n">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="F324" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G324" s="3" t="n">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="H324" s="2" t="n">
-        <v>2669752.87</v>
+        <v>2132488.45</v>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPIF, OSSURRBAC</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
     </row>
@@ -14792,26 +14792,26 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>ARNODO DANIEL</t>
+          <t>SALOMON MARIO RAMIRO</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D325" s="2" t="n">
-        <v>2143488.45</v>
+        <v>1771000</v>
       </c>
       <c r="E325" s="2" t="n">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="F325" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G325" s="3" t="n">
-        <v>0.0051</v>
+        <v>0</v>
       </c>
       <c r="H325" s="2" t="n">
-        <v>2132488.45</v>
+        <v>1771000</v>
       </c>
       <c r="I325" t="inlineStr">
         <is>
@@ -14827,14 +14827,14 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>PEREIRA ALEJANDRO MANUEL</t>
+          <t>CIDI S.A</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D326" s="2" t="n">
-        <v>475500</v>
+        <v>1677951.58</v>
       </c>
       <c r="E326" s="2" t="n">
         <v>0</v>
@@ -14846,11 +14846,11 @@
         <v>0</v>
       </c>
       <c r="H326" s="2" t="n">
-        <v>2021280.98</v>
+        <v>1677951.58</v>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPEVIC, OSPIF, OSPLYFC, OSSURRBAC</t>
         </is>
       </c>
     </row>
@@ -14862,30 +14862,30 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>CIRCULO MEDICO REGIONAL RIO TERCERO</t>
+          <t>RESONANCIA MAGNETICA SRL</t>
         </is>
       </c>
       <c r="C327" t="n">
         <v>5</v>
       </c>
       <c r="D327" s="2" t="n">
-        <v>4645450.64</v>
+        <v>1635936.24</v>
       </c>
       <c r="E327" s="2" t="n">
-        <v>12892.04</v>
+        <v>0</v>
       </c>
       <c r="F327" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G327" s="3" t="n">
-        <v>0.0028</v>
+        <v>0</v>
       </c>
       <c r="H327" s="2" t="n">
-        <v>2007679.68</v>
+        <v>1635936.24</v>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPLYFC, OSPM</t>
+          <t>OSPEVIC, OSPIF, OSSURRBAC</t>
         </is>
       </c>
     </row>
@@ -14897,30 +14897,30 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>LOYEAU EDUARDO JORGE</t>
+          <t>GPAL BIOQUIMICA CLINICA S.A.S.</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D328" s="2" t="n">
-        <v>953000</v>
+        <v>1586730</v>
       </c>
       <c r="E328" s="2" t="n">
-        <v>38000</v>
+        <v>0</v>
       </c>
       <c r="F328" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G328" s="3" t="n">
-        <v>0.0399</v>
+        <v>0</v>
       </c>
       <c r="H328" s="2" t="n">
-        <v>1925000</v>
+        <v>1586730</v>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPEVIC, OSPIF, OSPLYFC, OSSURRBAC</t>
         </is>
       </c>
     </row>
@@ -14932,14 +14932,14 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>SANATORIO CRUZ AZUL SRL</t>
+          <t>IMAGENES MEDICAS S.R.L.</t>
         </is>
       </c>
       <c r="C329" t="n">
         <v>1</v>
       </c>
       <c r="D329" s="2" t="n">
-        <v>30640</v>
+        <v>1132791.13</v>
       </c>
       <c r="E329" s="2" t="n">
         <v>0</v>
@@ -14951,11 +14951,11 @@
         <v>0</v>
       </c>
       <c r="H329" s="2" t="n">
-        <v>1779717.61</v>
+        <v>1132791.13</v>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
     </row>
@@ -14967,14 +14967,14 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>ROGGERO NORMA BEATRIZ</t>
+          <t>MIRANDA VERONICA ANABEL</t>
         </is>
       </c>
       <c r="C330" t="n">
         <v>1</v>
       </c>
       <c r="D330" s="2" t="n">
-        <v>419639.94</v>
+        <v>1067000</v>
       </c>
       <c r="E330" s="2" t="n">
         <v>0</v>
@@ -14986,7 +14986,7 @@
         <v>0</v>
       </c>
       <c r="H330" s="2" t="n">
-        <v>1771000</v>
+        <v>1067000</v>
       </c>
       <c r="I330" t="inlineStr">
         <is>
@@ -15002,14 +15002,14 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>EQUILIBRE SALUD S.A.S.</t>
+          <t>G.M. AGRUPACION DE COLABORACION.</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D331" s="2" t="n">
-        <v>340229.2</v>
+        <v>1042650.99</v>
       </c>
       <c r="E331" s="2" t="n">
         <v>0</v>
@@ -15021,7 +15021,7 @@
         <v>0</v>
       </c>
       <c r="H331" s="2" t="n">
-        <v>1707842.34</v>
+        <v>1042650.99</v>
       </c>
       <c r="I331" t="inlineStr">
         <is>
@@ -15037,14 +15037,14 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>CIDI S.A</t>
+          <t>COSEME SA</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D332" s="2" t="n">
-        <v>1677951.58</v>
+        <v>1007533.66</v>
       </c>
       <c r="E332" s="2" t="n">
         <v>0</v>
@@ -15056,11 +15056,11 @@
         <v>0</v>
       </c>
       <c r="H332" s="2" t="n">
-        <v>1677951.58</v>
+        <v>1007533.66</v>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPIF, OSPLYFC, OSSURRBAC</t>
+          <t>OSPEVIC, OSPIF</t>
         </is>
       </c>
     </row>
@@ -15072,14 +15072,14 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>ESTIX S.A.S.</t>
+          <t>UROLIT SA</t>
         </is>
       </c>
       <c r="C333" t="n">
         <v>1</v>
       </c>
       <c r="D333" s="2" t="n">
-        <v>528390.64</v>
+        <v>987646</v>
       </c>
       <c r="E333" s="2" t="n">
         <v>0</v>
@@ -15091,11 +15091,11 @@
         <v>0</v>
       </c>
       <c r="H333" s="2" t="n">
-        <v>1632036</v>
+        <v>987646</v>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>OSPLYFC</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
     </row>
@@ -15107,26 +15107,26 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>SANATORIO DEL SALVADOR PRIVADO SA</t>
+          <t>CENTRO PRIVADO TOMOGRAFIA COMPUTADA CORDOBA SOC AN</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D334" s="2" t="n">
-        <v>3269563.53</v>
+        <v>932998.15</v>
       </c>
       <c r="E334" s="2" t="n">
-        <v>20519.13</v>
+        <v>0</v>
       </c>
       <c r="F334" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G334" s="3" t="n">
-        <v>0.0063</v>
+        <v>0</v>
       </c>
       <c r="H334" s="2" t="n">
-        <v>1600618.21</v>
+        <v>932998.15</v>
       </c>
       <c r="I334" t="inlineStr">
         <is>
@@ -15142,14 +15142,14 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO SALUD-CONSORCIO DE COOPERACION</t>
+          <t>RUFFIN ESTEBAN MAURICIO</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D335" s="2" t="n">
-        <v>13685686.47</v>
+        <v>930864.78</v>
       </c>
       <c r="E335" s="2" t="n">
         <v>0</v>
@@ -15161,11 +15161,11 @@
         <v>0</v>
       </c>
       <c r="H335" s="2" t="n">
-        <v>1593573.76</v>
+        <v>930864.78</v>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPIF, OSPM</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
     </row>
@@ -15177,30 +15177,30 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>GRUPO OPTICO SA</t>
+          <t>LOYEAU EDUARDO JORGE</t>
         </is>
       </c>
       <c r="C336" t="n">
         <v>2</v>
       </c>
       <c r="D336" s="2" t="n">
-        <v>402720</v>
+        <v>953000</v>
       </c>
       <c r="E336" s="2" t="n">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="F336" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G336" s="3" t="n">
-        <v>0</v>
+        <v>0.0399</v>
       </c>
       <c r="H336" s="2" t="n">
-        <v>1452183.07</v>
+        <v>915000</v>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
     </row>
@@ -15212,30 +15212,30 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA INTEGRAL DE PSIQUIATRIA SAN NICOLA</t>
+          <t>SALUD INTEGRAL SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D337" s="2" t="n">
-        <v>6563200</v>
+        <v>915313</v>
       </c>
       <c r="E337" s="2" t="n">
-        <v>0</v>
+        <v>3372</v>
       </c>
       <c r="F337" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G337" s="3" t="n">
-        <v>0</v>
+        <v>0.0037</v>
       </c>
       <c r="H337" s="2" t="n">
-        <v>1429396.13</v>
+        <v>911941</v>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPIF, OSPLYFC</t>
+          <t>OSPEVIC, OSPLYFC, OSSURRBAC</t>
         </is>
       </c>
     </row>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>SOP S R L</t>
+          <t>MARIN DANIEL ALBERTO</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D338" s="2" t="n">
-        <v>5940972</v>
+        <v>858000</v>
       </c>
       <c r="E338" s="2" t="n">
         <v>0</v>
@@ -15266,11 +15266,11 @@
         <v>0</v>
       </c>
       <c r="H338" s="2" t="n">
-        <v>1231646</v>
+        <v>858000</v>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
     </row>
@@ -15282,14 +15282,14 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>FUNDACION FECUNDART</t>
+          <t>EDUARDO JORGE LOYEAU</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D339" s="2" t="n">
-        <v>216159.6</v>
+        <v>825000</v>
       </c>
       <c r="E339" s="2" t="n">
         <v>0</v>
@@ -15301,7 +15301,7 @@
         <v>0</v>
       </c>
       <c r="H339" s="2" t="n">
-        <v>1063650.99</v>
+        <v>825000</v>
       </c>
       <c r="I339" t="inlineStr">
         <is>
@@ -15317,14 +15317,14 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>MOLINA MARIA FERNANDA</t>
+          <t>SOLBO S.A.S.</t>
         </is>
       </c>
       <c r="C340" t="n">
         <v>2</v>
       </c>
       <c r="D340" s="2" t="n">
-        <v>225300</v>
+        <v>805375.03</v>
       </c>
       <c r="E340" s="2" t="n">
         <v>0</v>
@@ -15336,11 +15336,11 @@
         <v>0</v>
       </c>
       <c r="H340" s="2" t="n">
-        <v>961957.8</v>
+        <v>805375.03</v>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSSURRBAC</t>
+          <t>OSPEVIC, OSPIF</t>
         </is>
       </c>
     </row>
@@ -15352,14 +15352,14 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>COSEME SA</t>
+          <t>RIOS DARIO EDUARDO</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D341" s="2" t="n">
-        <v>1007533.66</v>
+        <v>780862.08</v>
       </c>
       <c r="E341" s="2" t="n">
         <v>0</v>
@@ -15371,11 +15371,11 @@
         <v>0</v>
       </c>
       <c r="H341" s="2" t="n">
-        <v>946667.3100000001</v>
+        <v>780862.08</v>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
     </row>
@@ -15387,14 +15387,14 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA SANTA MARIA S.A.</t>
+          <t>DE LA VILLA SERVICIOS ASISTENCIALES S.A.</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D342" s="2" t="n">
-        <v>577698.5600000001</v>
+        <v>682703.64</v>
       </c>
       <c r="E342" s="2" t="n">
         <v>0</v>
@@ -15406,11 +15406,11 @@
         <v>0</v>
       </c>
       <c r="H342" s="2" t="n">
-        <v>938447.38</v>
+        <v>682703.64</v>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPIF</t>
+          <t>OSPIF, OSPLYFC, OSSURRBAC</t>
         </is>
       </c>
     </row>
@@ -15422,14 +15422,14 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>CENTRO PRIVADO TOMOGRAFIA COMPUTADA CORDOBA SOC AN</t>
+          <t>SANATORIO PARQUE S A</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D343" s="2" t="n">
-        <v>932998.15</v>
+        <v>677538.41</v>
       </c>
       <c r="E343" s="2" t="n">
         <v>0</v>
@@ -15441,11 +15441,11 @@
         <v>0</v>
       </c>
       <c r="H343" s="2" t="n">
-        <v>932998.15</v>
+        <v>677538.41</v>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPIF, OSPM</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
     </row>
@@ -15457,14 +15457,14 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA CARAFFA SRL</t>
+          <t>TOLEDO YOHANA ELIZABETH</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D344" s="2" t="n">
-        <v>9755631.640000001</v>
+        <v>662359.2</v>
       </c>
       <c r="E344" s="2" t="n">
         <v>0</v>
@@ -15476,7 +15476,7 @@
         <v>0</v>
       </c>
       <c r="H344" s="2" t="n">
-        <v>909840.84</v>
+        <v>662359.2</v>
       </c>
       <c r="I344" t="inlineStr">
         <is>
@@ -15492,14 +15492,14 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ROENTGEN S A</t>
+          <t>FUNDACION CENTRO PREVENCION Y ATENCION CONTRA BULI</t>
         </is>
       </c>
       <c r="C345" t="n">
         <v>1</v>
       </c>
       <c r="D345" s="2" t="n">
-        <v>508186.56</v>
+        <v>600000</v>
       </c>
       <c r="E345" s="2" t="n">
         <v>0</v>
@@ -15511,11 +15511,11 @@
         <v>0</v>
       </c>
       <c r="H345" s="2" t="n">
-        <v>909000</v>
+        <v>600000</v>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
     </row>
@@ -15527,14 +15527,14 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>COCCO NATALIA</t>
+          <t>EL JUNCO SERVICIOS SOCIALES SA</t>
         </is>
       </c>
       <c r="C346" t="n">
         <v>2</v>
       </c>
       <c r="D346" s="2" t="n">
-        <v>440700.06</v>
+        <v>587837</v>
       </c>
       <c r="E346" s="2" t="n">
         <v>0</v>
@@ -15546,11 +15546,11 @@
         <v>0</v>
       </c>
       <c r="H346" s="2" t="n">
-        <v>870311.26</v>
+        <v>587837</v>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPEVIC, OSPLYFC</t>
         </is>
       </c>
     </row>
@@ -15562,14 +15562,14 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>RUFFIN ESTEBAN MAURICIO</t>
+          <t>CLINICA PRIVADA SANTA MARIA S.A.</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D347" s="2" t="n">
-        <v>930864.78</v>
+        <v>577698.5600000001</v>
       </c>
       <c r="E347" s="2" t="n">
         <v>0</v>
@@ -15581,11 +15581,11 @@
         <v>0</v>
       </c>
       <c r="H347" s="2" t="n">
-        <v>851263</v>
+        <v>577698.5600000001</v>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPEVIC, OSPIF</t>
         </is>
       </c>
     </row>
@@ -15597,14 +15597,14 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>GPAL BIOQUIMICA CLINICA S.A.S.</t>
+          <t>CARNERO JORGE ALBERTO DEL VALLE</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D348" s="2" t="n">
-        <v>1586730</v>
+        <v>576000</v>
       </c>
       <c r="E348" s="2" t="n">
         <v>0</v>
@@ -15616,11 +15616,11 @@
         <v>0</v>
       </c>
       <c r="H348" s="2" t="n">
-        <v>822400</v>
+        <v>576000</v>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPIF, OSPLYFC, OSSURRBAC</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
     </row>
@@ -15632,26 +15632,26 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>LECOUSER S.A.</t>
+          <t>ARRAMBIDE MARIA DE LA PAZ</t>
         </is>
       </c>
       <c r="C349" t="n">
         <v>1</v>
       </c>
       <c r="D349" s="2" t="n">
-        <v>231000</v>
+        <v>570146.24</v>
       </c>
       <c r="E349" s="2" t="n">
-        <v>66000</v>
+        <v>0</v>
       </c>
       <c r="F349" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G349" s="3" t="n">
-        <v>0.2857</v>
+        <v>0</v>
       </c>
       <c r="H349" s="2" t="n">
-        <v>795000</v>
+        <v>570146.24</v>
       </c>
       <c r="I349" t="inlineStr">
         <is>
@@ -15667,14 +15667,14 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>GILETTA CLAUDIA VIVIANA</t>
+          <t>CEMO S.A.</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D350" s="2" t="n">
-        <v>441000</v>
+        <v>558975.8</v>
       </c>
       <c r="E350" s="2" t="n">
         <v>0</v>
@@ -15686,7 +15686,7 @@
         <v>0</v>
       </c>
       <c r="H350" s="2" t="n">
-        <v>733125</v>
+        <v>558975.8</v>
       </c>
       <c r="I350" t="inlineStr">
         <is>
@@ -15702,14 +15702,14 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>SICOT MELINA PAULA</t>
+          <t>CLINICA CHUTRO S R L</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D351" s="2" t="n">
-        <v>68000</v>
+        <v>553173.98</v>
       </c>
       <c r="E351" s="2" t="n">
         <v>0</v>
@@ -15721,11 +15721,11 @@
         <v>0</v>
       </c>
       <c r="H351" s="2" t="n">
-        <v>725065.77</v>
+        <v>553173.98</v>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPIF, OSSURRBAC</t>
         </is>
       </c>
     </row>
@@ -15737,14 +15737,14 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>DE LA VILLA SERVICIOS ASISTENCIALES S.A.</t>
+          <t>ESTIX S.A.S.</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D352" s="2" t="n">
-        <v>682703.64</v>
+        <v>528390.64</v>
       </c>
       <c r="E352" s="2" t="n">
         <v>0</v>
@@ -15756,11 +15756,11 @@
         <v>0</v>
       </c>
       <c r="H352" s="2" t="n">
-        <v>698495.75</v>
+        <v>528390.64</v>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>OSPIF, OSPLYFC, OSSURRBAC</t>
+          <t>OSPLYFC</t>
         </is>
       </c>
     </row>
@@ -15772,14 +15772,14 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>FESER MARIA LAURA</t>
+          <t>ROENTGEN S A</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D353" s="2" t="n">
-        <v>120000</v>
+        <v>508186.56</v>
       </c>
       <c r="E353" s="2" t="n">
         <v>0</v>
@@ -15791,11 +15791,11 @@
         <v>0</v>
       </c>
       <c r="H353" s="2" t="n">
-        <v>627370</v>
+        <v>508186.56</v>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
     </row>
@@ -15807,14 +15807,14 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>CARNERO JORGE ALBERTO DEL VALLE</t>
+          <t>NIEVA MARIA EMILIA</t>
         </is>
       </c>
       <c r="C354" t="n">
         <v>1</v>
       </c>
       <c r="D354" s="2" t="n">
-        <v>576000</v>
+        <v>486457.8</v>
       </c>
       <c r="E354" s="2" t="n">
         <v>0</v>
@@ -15826,7 +15826,7 @@
         <v>0</v>
       </c>
       <c r="H354" s="2" t="n">
-        <v>576000</v>
+        <v>486457.8</v>
       </c>
       <c r="I354" t="inlineStr">
         <is>
@@ -15842,14 +15842,14 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>ARRAMBIDE MARIA DE LA PAZ</t>
+          <t>PEREIRA ALEJANDRO MANUEL</t>
         </is>
       </c>
       <c r="C355" t="n">
         <v>1</v>
       </c>
       <c r="D355" s="2" t="n">
-        <v>570146.24</v>
+        <v>475500</v>
       </c>
       <c r="E355" s="2" t="n">
         <v>0</v>
@@ -15861,7 +15861,7 @@
         <v>0</v>
       </c>
       <c r="H355" s="2" t="n">
-        <v>570146.24</v>
+        <v>475500</v>
       </c>
       <c r="I355" t="inlineStr">
         <is>
@@ -15877,14 +15877,14 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>CEMO S.A.</t>
+          <t>SANATORIO MORRA S A</t>
         </is>
       </c>
       <c r="C356" t="n">
         <v>2</v>
       </c>
       <c r="D356" s="2" t="n">
-        <v>558975.8</v>
+        <v>469707.97</v>
       </c>
       <c r="E356" s="2" t="n">
         <v>0</v>
@@ -15896,11 +15896,11 @@
         <v>0</v>
       </c>
       <c r="H356" s="2" t="n">
-        <v>558975.8</v>
+        <v>469707.97</v>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF, OSPM</t>
         </is>
       </c>
     </row>
@@ -15982,14 +15982,14 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>SOLBO S.A.S.</t>
+          <t>COLEGIO MED REG DEL SUR DE CBA</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D359" s="2" t="n">
-        <v>805375.03</v>
+        <v>457115.8</v>
       </c>
       <c r="E359" s="2" t="n">
         <v>0</v>
@@ -16001,11 +16001,11 @@
         <v>0</v>
       </c>
       <c r="H359" s="2" t="n">
-        <v>451959.2</v>
+        <v>457115.8</v>
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPIF</t>
+          <t>OSPIF</t>
         </is>
       </c>
     </row>
@@ -16017,14 +16017,14 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>G.M. AGRUPACION DE COLABORACION.</t>
+          <t>GILETTA CLAUDIA VIVIANA</t>
         </is>
       </c>
       <c r="C360" t="n">
         <v>1</v>
       </c>
       <c r="D360" s="2" t="n">
-        <v>1042650.99</v>
+        <v>441000</v>
       </c>
       <c r="E360" s="2" t="n">
         <v>0</v>
@@ -16040,7 +16040,7 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
     </row>
@@ -16052,14 +16052,14 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>REYLES S.A.</t>
+          <t>COCCO NATALIA</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D361" s="2" t="n">
-        <v>9705.6</v>
+        <v>440700.06</v>
       </c>
       <c r="E361" s="2" t="n">
         <v>0</v>
@@ -16071,11 +16071,11 @@
         <v>0</v>
       </c>
       <c r="H361" s="2" t="n">
-        <v>440000</v>
+        <v>440700.06</v>
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>OSPLYFC</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
     </row>
@@ -16087,30 +16087,30 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>GARRONE JESICA VALERIA</t>
+          <t>RUCCI SILVANA LORENA</t>
         </is>
       </c>
       <c r="C362" t="n">
         <v>1</v>
       </c>
       <c r="D362" s="2" t="n">
-        <v>23100</v>
+        <v>440000</v>
       </c>
       <c r="E362" s="2" t="n">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="F362" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G362" s="3" t="n">
-        <v>0.09089999999999999</v>
+        <v>0</v>
       </c>
       <c r="H362" s="2" t="n">
-        <v>433925</v>
+        <v>440000</v>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>OSSURRBAC</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
     </row>
@@ -16122,30 +16122,30 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>L A C E SA</t>
+          <t>ROGGERO NORMA BEATRIZ</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D363" s="2" t="n">
-        <v>286321.28</v>
+        <v>419639.94</v>
       </c>
       <c r="E363" s="2" t="n">
-        <v>83877.12</v>
+        <v>0</v>
       </c>
       <c r="F363" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G363" s="3" t="n">
-        <v>0.2929</v>
+        <v>0</v>
       </c>
       <c r="H363" s="2" t="n">
-        <v>387131.2</v>
+        <v>419639.94</v>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPIF, OSPM</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
     </row>
@@ -16157,14 +16157,14 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>HEREDIA MARIA PAULA</t>
+          <t>COLEGIO MEDICO DE OLIVA</t>
         </is>
       </c>
       <c r="C364" t="n">
         <v>1</v>
       </c>
       <c r="D364" s="2" t="n">
-        <v>319391.94</v>
+        <v>413195.46</v>
       </c>
       <c r="E364" s="2" t="n">
         <v>0</v>
@@ -16176,11 +16176,11 @@
         <v>0</v>
       </c>
       <c r="H364" s="2" t="n">
-        <v>272384.5</v>
+        <v>413195.46</v>
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
     </row>
@@ -16192,30 +16192,30 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>COLEGIO PSICOLOGOS DE LA PROV. DE CORDOBA</t>
+          <t>GRUPO OPTICO SA</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D365" s="2" t="n">
-        <v>131040</v>
+        <v>402720</v>
       </c>
       <c r="E365" s="2" t="n">
-        <v>52416</v>
+        <v>0</v>
       </c>
       <c r="F365" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G365" s="3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H365" s="2" t="n">
-        <v>267595.91</v>
+        <v>402720</v>
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPEVIC, OSPIF</t>
         </is>
       </c>
     </row>
@@ -16227,14 +16227,14 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>EDUARDO JORGE LOYEAU</t>
+          <t>UNIDAD DIGESTIVA BAISTROCCHI S.R.L.</t>
         </is>
       </c>
       <c r="C366" t="n">
         <v>1</v>
       </c>
       <c r="D366" s="2" t="n">
-        <v>825000</v>
+        <v>347600</v>
       </c>
       <c r="E366" s="2" t="n">
         <v>0</v>
@@ -16246,7 +16246,7 @@
         <v>0</v>
       </c>
       <c r="H366" s="2" t="n">
-        <v>260629</v>
+        <v>347600</v>
       </c>
       <c r="I366" t="inlineStr">
         <is>
@@ -16262,14 +16262,14 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>REBERTE MARICEL EDITH</t>
+          <t>EQUILIBRE SALUD S.A.S.</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D367" s="2" t="n">
-        <v>216000</v>
+        <v>340229.2</v>
       </c>
       <c r="E367" s="2" t="n">
         <v>0</v>
@@ -16281,11 +16281,11 @@
         <v>0</v>
       </c>
       <c r="H367" s="2" t="n">
-        <v>244925.7</v>
+        <v>340229.2</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
     </row>
@@ -16297,30 +16297,30 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>CENTRO DE BIOQUIMICOS REGIONAL DE RIO CUARTO</t>
+          <t>HEREDIA MARIA PAULA</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D368" s="2" t="n">
-        <v>344181.5</v>
+        <v>319391.94</v>
       </c>
       <c r="E368" s="2" t="n">
-        <v>117097.5</v>
+        <v>0</v>
       </c>
       <c r="F368" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G368" s="3" t="n">
-        <v>0.3402000000000001</v>
+        <v>0</v>
       </c>
       <c r="H368" s="2" t="n">
-        <v>227084</v>
+        <v>319391.94</v>
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
     </row>
@@ -16332,14 +16332,14 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>MARIN DANIEL ALBERTO</t>
+          <t>SANCHEZ LUIS FERNANDO</t>
         </is>
       </c>
       <c r="C369" t="n">
         <v>1</v>
       </c>
       <c r="D369" s="2" t="n">
-        <v>858000</v>
+        <v>260000</v>
       </c>
       <c r="E369" s="2" t="n">
         <v>0</v>
@@ -16351,7 +16351,7 @@
         <v>0</v>
       </c>
       <c r="H369" s="2" t="n">
-        <v>200000</v>
+        <v>260000</v>
       </c>
       <c r="I369" t="inlineStr">
         <is>
@@ -16367,26 +16367,26 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>BUGIA MARCELO LUIS</t>
+          <t>VILLALBA MARIA EUGENIA</t>
         </is>
       </c>
       <c r="C370" t="n">
         <v>1</v>
       </c>
       <c r="D370" s="2" t="n">
-        <v>198000</v>
+        <v>244000</v>
       </c>
       <c r="E370" s="2" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="F370" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G370" s="3" t="n">
-        <v>0.0455</v>
+        <v>0</v>
       </c>
       <c r="H370" s="2" t="n">
-        <v>189000</v>
+        <v>244000</v>
       </c>
       <c r="I370" t="inlineStr">
         <is>
@@ -16402,14 +16402,14 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>FUNDACION CENTRO PREVENCION Y ATENCION CONTRA BULI</t>
+          <t>CLINICA PRIVADA JESUS MARIA DR ANIBAL LUIS VIALE S</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D371" s="2" t="n">
-        <v>600000</v>
+        <v>231696.13</v>
       </c>
       <c r="E371" s="2" t="n">
         <v>0</v>
@@ -16421,11 +16421,11 @@
         <v>0</v>
       </c>
       <c r="H371" s="2" t="n">
-        <v>188789.6</v>
+        <v>231696.13</v>
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPEVIC, OSPIF</t>
         </is>
       </c>
     </row>
@@ -16437,30 +16437,30 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>AGUERO RAMACCIONI</t>
+          <t>CENTRO DE BIOQUIMICOS REGIONAL DE RIO CUARTO</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D372" s="2" t="n">
-        <v>186547.02</v>
+        <v>344181.5</v>
       </c>
       <c r="E372" s="2" t="n">
-        <v>0</v>
+        <v>117097.5</v>
       </c>
       <c r="F372" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G372" s="3" t="n">
-        <v>0</v>
+        <v>0.3402000000000001</v>
       </c>
       <c r="H372" s="2" t="n">
-        <v>186547.02</v>
+        <v>227084</v>
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPEVIC, OSPIF</t>
         </is>
       </c>
     </row>
@@ -16472,14 +16472,14 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>BARIATRICA S.A. S. A.</t>
+          <t>MOLINA MARIA FERNANDA</t>
         </is>
       </c>
       <c r="C373" t="n">
         <v>2</v>
       </c>
       <c r="D373" s="2" t="n">
-        <v>173580</v>
+        <v>225300</v>
       </c>
       <c r="E373" s="2" t="n">
         <v>0</v>
@@ -16491,11 +16491,11 @@
         <v>0</v>
       </c>
       <c r="H373" s="2" t="n">
-        <v>173580</v>
+        <v>225300</v>
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPEVIC, OSSURRBAC</t>
         </is>
       </c>
     </row>
@@ -16507,14 +16507,14 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA DEAN FUNES S.R.L.</t>
+          <t>FUNDACION FECUNDART</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D374" s="2" t="n">
-        <v>2850705.51</v>
+        <v>216159.6</v>
       </c>
       <c r="E374" s="2" t="n">
         <v>0</v>
@@ -16526,7 +16526,7 @@
         <v>0</v>
       </c>
       <c r="H374" s="2" t="n">
-        <v>158885.19</v>
+        <v>216159.6</v>
       </c>
       <c r="I374" t="inlineStr">
         <is>
@@ -16542,14 +16542,14 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>IMAGENES MEDICAS S.R.L.</t>
+          <t>REBERTE MARICEL EDITH</t>
         </is>
       </c>
       <c r="C375" t="n">
         <v>1</v>
       </c>
       <c r="D375" s="2" t="n">
-        <v>1132791.13</v>
+        <v>216000</v>
       </c>
       <c r="E375" s="2" t="n">
         <v>0</v>
@@ -16561,7 +16561,7 @@
         <v>0</v>
       </c>
       <c r="H375" s="2" t="n">
-        <v>136849.56</v>
+        <v>216000</v>
       </c>
       <c r="I375" t="inlineStr">
         <is>
@@ -16577,14 +16577,14 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>CARDOSO FERNANDO MIGUEL</t>
+          <t>DELFINO IRINA MARIEL</t>
         </is>
       </c>
       <c r="C376" t="n">
         <v>1</v>
       </c>
       <c r="D376" s="2" t="n">
-        <v>121500</v>
+        <v>204000</v>
       </c>
       <c r="E376" s="2" t="n">
         <v>0</v>
@@ -16596,7 +16596,7 @@
         <v>0</v>
       </c>
       <c r="H376" s="2" t="n">
-        <v>121500</v>
+        <v>204000</v>
       </c>
       <c r="I376" t="inlineStr">
         <is>
@@ -16612,30 +16612,30 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>FEDERACION DE BIOQUIMICOS DE LA PROVINCIA DE CORDO</t>
+          <t>L A C E SA</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D377" s="2" t="n">
-        <v>2565889.5</v>
+        <v>286321.28</v>
       </c>
       <c r="E377" s="2" t="n">
-        <v>0</v>
+        <v>83877.12</v>
       </c>
       <c r="F377" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G377" s="3" t="n">
-        <v>0</v>
+        <v>0.2929</v>
       </c>
       <c r="H377" s="2" t="n">
-        <v>120000</v>
+        <v>202444.16</v>
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPIF</t>
+          <t>OSPEVIC, OSPIF, OSPM</t>
         </is>
       </c>
     </row>
@@ -16647,26 +16647,26 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>LOYEAU ARIEL MAXIMILANO</t>
+          <t>BUGIA MARCELO LUIS</t>
         </is>
       </c>
       <c r="C378" t="n">
         <v>1</v>
       </c>
       <c r="D378" s="2" t="n">
-        <v>160000</v>
+        <v>198000</v>
       </c>
       <c r="E378" s="2" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="F378" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G378" s="3" t="n">
-        <v>0</v>
+        <v>0.0455</v>
       </c>
       <c r="H378" s="2" t="n">
-        <v>120000</v>
+        <v>189000</v>
       </c>
       <c r="I378" t="inlineStr">
         <is>
@@ -16682,14 +16682,14 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA JESUS MARIA DR ANIBAL LUIS VIALE S</t>
+          <t>AGUERO RAMACCIONI</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D379" s="2" t="n">
-        <v>231696.13</v>
+        <v>186547.02</v>
       </c>
       <c r="E379" s="2" t="n">
         <v>0</v>
@@ -16701,11 +16701,11 @@
         <v>0</v>
       </c>
       <c r="H379" s="2" t="n">
-        <v>117538.28</v>
+        <v>186547.02</v>
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
     </row>
@@ -16717,14 +16717,14 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>EL JUNCO SERVICIOS SOCIALES SA</t>
+          <t>BARIATRICA S.A. S. A.</t>
         </is>
       </c>
       <c r="C380" t="n">
         <v>2</v>
       </c>
       <c r="D380" s="2" t="n">
-        <v>587837</v>
+        <v>173580</v>
       </c>
       <c r="E380" s="2" t="n">
         <v>0</v>
@@ -16736,11 +16736,11 @@
         <v>0</v>
       </c>
       <c r="H380" s="2" t="n">
-        <v>94631</v>
+        <v>173580</v>
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPLYFC</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
     </row>
@@ -16752,26 +16752,26 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>NIEVA MARIA EMILIA</t>
+          <t>LECOUSER S.A.</t>
         </is>
       </c>
       <c r="C381" t="n">
         <v>1</v>
       </c>
       <c r="D381" s="2" t="n">
-        <v>486457.8</v>
+        <v>231000</v>
       </c>
       <c r="E381" s="2" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="F381" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G381" s="3" t="n">
-        <v>0</v>
+        <v>0.2857</v>
       </c>
       <c r="H381" s="2" t="n">
-        <v>90667.33</v>
+        <v>165000</v>
       </c>
       <c r="I381" t="inlineStr">
         <is>
@@ -16787,14 +16787,14 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>PROYECTOS INNOVADORES S R L</t>
+          <t>LOYEAU ARIEL MAXIMILANO</t>
         </is>
       </c>
       <c r="C382" t="n">
         <v>1</v>
       </c>
       <c r="D382" s="2" t="n">
-        <v>3630000</v>
+        <v>160000</v>
       </c>
       <c r="E382" s="2" t="n">
         <v>0</v>
@@ -16806,7 +16806,7 @@
         <v>0</v>
       </c>
       <c r="H382" s="2" t="n">
-        <v>83094.35000000001</v>
+        <v>160000</v>
       </c>
       <c r="I382" t="inlineStr">
         <is>
@@ -16822,14 +16822,14 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>COLEGIO MEDICO DE OLIVA</t>
+          <t>CLINICA PRIVADA DE LA CIUDAD SOC RESP LTDA</t>
         </is>
       </c>
       <c r="C383" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D383" s="2" t="n">
-        <v>413195.46</v>
+        <v>159125.42</v>
       </c>
       <c r="E383" s="2" t="n">
         <v>0</v>
@@ -16841,11 +16841,11 @@
         <v>0</v>
       </c>
       <c r="H383" s="2" t="n">
-        <v>78624</v>
+        <v>159125.42</v>
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC, OSPIF, OSPLYFC, OSSURRBAC</t>
         </is>
       </c>
     </row>
@@ -16857,30 +16857,30 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO ROENTGEN S.R.L.</t>
+          <t>CARDOSO FERNANDO MIGUEL</t>
         </is>
       </c>
       <c r="C384" t="n">
         <v>1</v>
       </c>
       <c r="D384" s="2" t="n">
-        <v>82131.56</v>
+        <v>121500</v>
       </c>
       <c r="E384" s="2" t="n">
-        <v>11179.68</v>
+        <v>0</v>
       </c>
       <c r="F384" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G384" s="3" t="n">
-        <v>0.1361</v>
+        <v>0</v>
       </c>
       <c r="H384" s="2" t="n">
-        <v>70951.88</v>
+        <v>121500</v>
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
     </row>
@@ -16892,14 +16892,14 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>RUCCI SILVANA LORENA</t>
+          <t>FESER MARIA LAURA</t>
         </is>
       </c>
       <c r="C385" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D385" s="2" t="n">
-        <v>440000</v>
+        <v>120000</v>
       </c>
       <c r="E385" s="2" t="n">
         <v>0</v>
@@ -16911,7 +16911,7 @@
         <v>0</v>
       </c>
       <c r="H385" s="2" t="n">
-        <v>60678</v>
+        <v>120000</v>
       </c>
       <c r="I385" t="inlineStr">
         <is>
@@ -16927,14 +16927,14 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>COLEGIO MED REG DEL SUR DE CBA</t>
+          <t>CLINICA PRIVADA DE ESPECIALIDADES DE VILLA MARIA S</t>
         </is>
       </c>
       <c r="C386" t="n">
         <v>1</v>
       </c>
       <c r="D386" s="2" t="n">
-        <v>457115.8</v>
+        <v>82184.34</v>
       </c>
       <c r="E386" s="2" t="n">
         <v>0</v>
@@ -16946,7 +16946,7 @@
         <v>0</v>
       </c>
       <c r="H386" s="2" t="n">
-        <v>53488.34</v>
+        <v>82184.34</v>
       </c>
       <c r="I386" t="inlineStr">
         <is>
@@ -16962,14 +16962,14 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MEDICOS PATOLOGOS Y CITOPATOLOGOS DE</t>
+          <t>UNIVERSIDAD NACIONAL DE CORDOBA</t>
         </is>
       </c>
       <c r="C387" t="n">
         <v>2</v>
       </c>
       <c r="D387" s="2" t="n">
-        <v>43350</v>
+        <v>80000</v>
       </c>
       <c r="E387" s="2" t="n">
         <v>0</v>
@@ -16981,11 +16981,11 @@
         <v>0</v>
       </c>
       <c r="H387" s="2" t="n">
-        <v>43350</v>
+        <v>80000</v>
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPIF</t>
+          <t>OSPEVIC, OSSURRBAC</t>
         </is>
       </c>
     </row>
@@ -16997,30 +16997,30 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>AGUIRRE CARLOS ALBERTO</t>
+          <t>COLEGIO PSICOLOGOS DE LA PROV. DE CORDOBA</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D388" s="2" t="n">
-        <v>30000</v>
+        <v>131040</v>
       </c>
       <c r="E388" s="2" t="n">
-        <v>0</v>
+        <v>52416</v>
       </c>
       <c r="F388" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G388" s="3" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H388" s="2" t="n">
-        <v>30000</v>
+        <v>78624</v>
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPIF</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
     </row>
@@ -17032,30 +17032,30 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>MIRANDA VERONICA ANABEL</t>
+          <t>CENTRO MEDICO ROENTGEN S.R.L.</t>
         </is>
       </c>
       <c r="C389" t="n">
         <v>1</v>
       </c>
       <c r="D389" s="2" t="n">
-        <v>1067000</v>
+        <v>82131.56</v>
       </c>
       <c r="E389" s="2" t="n">
-        <v>0</v>
+        <v>11179.68</v>
       </c>
       <c r="F389" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G389" s="3" t="n">
-        <v>0</v>
+        <v>0.1361</v>
       </c>
       <c r="H389" s="2" t="n">
-        <v>25300</v>
+        <v>70951.88</v>
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
     </row>
@@ -17067,14 +17067,14 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA REGIONAL S R L</t>
+          <t>SICOT MELINA PAULA</t>
         </is>
       </c>
       <c r="C390" t="n">
         <v>1</v>
       </c>
       <c r="D390" s="2" t="n">
-        <v>60850</v>
+        <v>68000</v>
       </c>
       <c r="E390" s="2" t="n">
         <v>0</v>
@@ -17086,7 +17086,7 @@
         <v>0</v>
       </c>
       <c r="H390" s="2" t="n">
-        <v>23262.96</v>
+        <v>68000</v>
       </c>
       <c r="I390" t="inlineStr">
         <is>
@@ -17102,14 +17102,14 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>RIOS DARIO EDUARDO</t>
+          <t>CLINICA PRIVADA REGIONAL S R L</t>
         </is>
       </c>
       <c r="C391" t="n">
         <v>1</v>
       </c>
       <c r="D391" s="2" t="n">
-        <v>780862.08</v>
+        <v>60850</v>
       </c>
       <c r="E391" s="2" t="n">
         <v>0</v>
@@ -17121,11 +17121,11 @@
         <v>0</v>
       </c>
       <c r="H391" s="2" t="n">
-        <v>21864.78</v>
+        <v>60850</v>
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
     </row>
@@ -17156,7 +17156,7 @@
         <v>0</v>
       </c>
       <c r="H392" s="2" t="n">
-        <v>20945.33</v>
+        <v>53488.34</v>
       </c>
       <c r="I392" t="inlineStr">
         <is>
@@ -17172,14 +17172,14 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>CLINICA PRIVADA DE ESPECIALIDADES DE VILLA MARIA S</t>
+          <t>ASOCIACION DE MEDICOS PATOLOGOS Y CITOPATOLOGOS DE</t>
         </is>
       </c>
       <c r="C393" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D393" s="2" t="n">
-        <v>82184.34</v>
+        <v>43350</v>
       </c>
       <c r="E393" s="2" t="n">
         <v>0</v>
@@ -17191,11 +17191,11 @@
         <v>0</v>
       </c>
       <c r="H393" s="2" t="n">
-        <v>17983.88</v>
+        <v>43350</v>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>OSPIF</t>
+          <t>OSPEVIC, OSPIF</t>
         </is>
       </c>
     </row>
@@ -17207,14 +17207,14 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>ASOCIACION MUTUAL DOCTOR ESTEBAN LAUREANO MARADONA</t>
+          <t>DIAGNOSTICO Y TRATAMIENTO EN SALUD AMBULATORIA DEL</t>
         </is>
       </c>
       <c r="C394" t="n">
         <v>1</v>
       </c>
       <c r="D394" s="2" t="n">
-        <v>17302</v>
+        <v>39467</v>
       </c>
       <c r="E394" s="2" t="n">
         <v>0</v>
@@ -17226,7 +17226,7 @@
         <v>0</v>
       </c>
       <c r="H394" s="2" t="n">
-        <v>17302</v>
+        <v>39467</v>
       </c>
       <c r="I394" t="inlineStr">
         <is>
@@ -17242,14 +17242,14 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>TOLEDO YOHANA ELIZABETH</t>
+          <t>SANATORIO CRUZ AZUL SRL</t>
         </is>
       </c>
       <c r="C395" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D395" s="2" t="n">
-        <v>662359.2</v>
+        <v>30640</v>
       </c>
       <c r="E395" s="2" t="n">
         <v>0</v>
@@ -17261,11 +17261,11 @@
         <v>0</v>
       </c>
       <c r="H395" s="2" t="n">
-        <v>0</v>
+        <v>30640</v>
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPIF</t>
         </is>
       </c>
     </row>
@@ -17277,14 +17277,14 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>UNIDAD DIGESTIVA BAISTROCCHI S.R.L.</t>
+          <t>AGUIRRE CARLOS ALBERTO</t>
         </is>
       </c>
       <c r="C396" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D396" s="2" t="n">
-        <v>347600</v>
+        <v>30000</v>
       </c>
       <c r="E396" s="2" t="n">
         <v>0</v>
@@ -17296,11 +17296,11 @@
         <v>0</v>
       </c>
       <c r="H396" s="2" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPEVIC, OSPIF</t>
         </is>
       </c>
     </row>
@@ -17312,30 +17312,30 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD NACIONAL DE CORDOBA</t>
+          <t>GARRONE JESICA VALERIA</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D397" s="2" t="n">
-        <v>80000</v>
+        <v>23100</v>
       </c>
       <c r="E397" s="2" t="n">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="F397" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G397" s="3" t="n">
-        <v>0</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="H397" s="2" t="n">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSSURRBAC</t>
+          <t>OSSURRBAC</t>
         </is>
       </c>
     </row>
@@ -17347,14 +17347,14 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>UROLIT SA</t>
+          <t>ASOCIACION MUTUAL DOCTOR ESTEBAN LAUREANO MARADONA</t>
         </is>
       </c>
       <c r="C398" t="n">
         <v>1</v>
       </c>
       <c r="D398" s="2" t="n">
-        <v>987646</v>
+        <v>17302</v>
       </c>
       <c r="E398" s="2" t="n">
         <v>0</v>
@@ -17366,7 +17366,7 @@
         <v>0</v>
       </c>
       <c r="H398" s="2" t="n">
-        <v>0</v>
+        <v>17302</v>
       </c>
       <c r="I398" t="inlineStr">
         <is>
@@ -17382,14 +17382,14 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>VILLALBA MARIA EUGENIA</t>
+          <t>REYLES S.A.</t>
         </is>
       </c>
       <c r="C399" t="n">
         <v>1</v>
       </c>
       <c r="D399" s="2" t="n">
-        <v>244000</v>
+        <v>9705.6</v>
       </c>
       <c r="E399" s="2" t="n">
         <v>0</v>
@@ -17401,11 +17401,11 @@
         <v>0</v>
       </c>
       <c r="H399" s="2" t="n">
-        <v>0</v>
+        <v>9705.6</v>
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPLYFC</t>
         </is>
       </c>
     </row>
@@ -41174,21 +41174,34 @@
           <t>00004-00005797</t>
         </is>
       </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>Sin Clasificacion</t>
+          <t>Internado</t>
         </is>
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>GENERAL</t>
-        </is>
+          <t>OSPEVIC</t>
+        </is>
+      </c>
+      <c r="H531" t="n">
+        <v>184</v>
       </c>
       <c r="I531" s="2" t="n">
         <v>18785.59</v>
       </c>
       <c r="J531" s="2" t="n">
-        <v>0</v>
+        <v>5968</v>
       </c>
       <c r="K531" s="2" t="n">
         <v>0</v>
@@ -41213,24 +41226,37 @@
           <t>00004-00005798</t>
         </is>
       </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>Sin Clasificacion</t>
+          <t>Ambulatorio</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>GENERAL</t>
-        </is>
+          <t>OSPEVIC</t>
+        </is>
+      </c>
+      <c r="H532" t="n">
+        <v>184</v>
       </c>
       <c r="I532" s="2" t="n">
         <v>2262558.64</v>
       </c>
       <c r="J532" s="2" t="n">
-        <v>0</v>
+        <v>89417.86</v>
       </c>
       <c r="K532" s="2" t="n">
-        <v>0</v>
+        <v>286577.6</v>
       </c>
       <c r="L532" s="2" t="n">
         <v>1886563.18</v>
@@ -41252,15 +41278,28 @@
           <t>00004-00005799</t>
         </is>
       </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>Sin Clasificacion</t>
+          <t>Internado</t>
         </is>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>GENERAL</t>
-        </is>
+          <t>OSPLYFC</t>
+        </is>
+      </c>
+      <c r="H533" t="n">
+        <v>184</v>
       </c>
       <c r="I533" s="2" t="n">
         <v>975822.59</v>
@@ -41291,21 +41330,34 @@
           <t>00004-00005802</t>
         </is>
       </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>Sin Clasificacion</t>
+          <t>Ambulatorio</t>
         </is>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>GENERAL</t>
-        </is>
+          <t>OSPLYFC</t>
+        </is>
+      </c>
+      <c r="H534" t="n">
+        <v>184</v>
       </c>
       <c r="I534" s="2" t="n">
         <v>91594.2</v>
       </c>
       <c r="J534" s="2" t="n">
-        <v>0</v>
+        <v>87484.78</v>
       </c>
       <c r="K534" s="2" t="n">
         <v>0</v>
@@ -41330,15 +41382,28 @@
           <t>00004-00005806</t>
         </is>
       </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>Sin Clasificacion</t>
+          <t>Ambulatorio</t>
         </is>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>GENERAL</t>
-        </is>
+          <t>OSSURRBAC</t>
+        </is>
+      </c>
+      <c r="H535" t="n">
+        <v>184</v>
       </c>
       <c r="I535" s="2" t="n">
         <v>72025.24000000001</v>
@@ -41350,7 +41415,7 @@
         <v>0</v>
       </c>
       <c r="L535" s="2" t="n">
-        <v>10678.26</v>
+        <v>72025.24000000001</v>
       </c>
     </row>
     <row r="536">
@@ -41369,21 +41434,34 @@
           <t>00004-00005835</t>
         </is>
       </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>Sin Clasificacion</t>
+          <t>Ambulatorio</t>
         </is>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>GENERAL</t>
-        </is>
+          <t>OSSURRBAC</t>
+        </is>
+      </c>
+      <c r="H536" t="n">
+        <v>153</v>
       </c>
       <c r="I536" s="2" t="n">
         <v>59169.71</v>
       </c>
       <c r="J536" s="2" t="n">
-        <v>0</v>
+        <v>56891.45</v>
       </c>
       <c r="K536" s="2" t="n">
         <v>0</v>
@@ -41408,15 +41486,28 @@
           <t>00004-00005863</t>
         </is>
       </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>Sin Clasificacion</t>
+          <t>Ambulatorio</t>
         </is>
       </c>
       <c r="G537" t="inlineStr">
         <is>
-          <t>GENERAL</t>
-        </is>
+          <t>OSPEVIC</t>
+        </is>
+      </c>
+      <c r="H537" t="n">
+        <v>122</v>
       </c>
       <c r="I537" s="2" t="n">
         <v>667238.3199999999</v>
@@ -41428,7 +41519,7 @@
         <v>0</v>
       </c>
       <c r="L537" s="2" t="n">
-        <v>524929.36</v>
+        <v>667238.3199999999</v>
       </c>
     </row>
     <row r="538">
@@ -41447,15 +41538,28 @@
           <t>00004-00005864</t>
         </is>
       </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>Sin Clasificacion</t>
+          <t>Internado</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>GENERAL</t>
-        </is>
+          <t>OSPLYFC</t>
+        </is>
+      </c>
+      <c r="H538" t="n">
+        <v>122</v>
       </c>
       <c r="I538" s="2" t="n">
         <v>2203347.05</v>
@@ -41486,15 +41590,28 @@
           <t>00004-00005872</t>
         </is>
       </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>Sin Clasificacion</t>
+          <t>Internado</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>GENERAL</t>
-        </is>
+          <t>OSPEVIC</t>
+        </is>
+      </c>
+      <c r="H539" t="n">
+        <v>122</v>
       </c>
       <c r="I539" s="2" t="n">
         <v>26180.24</v>
@@ -41506,7 +41623,7 @@
         <v>0</v>
       </c>
       <c r="L539" s="2" t="n">
-        <v>4658.38</v>
+        <v>26180.24</v>
       </c>
     </row>
     <row r="540">
@@ -41525,15 +41642,28 @@
           <t>00004-00005884</t>
         </is>
       </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>Sin Clasificacion</t>
+          <t>Ambulatorio</t>
         </is>
       </c>
       <c r="G540" t="inlineStr">
         <is>
-          <t>GENERAL</t>
-        </is>
+          <t>OSPLYFC</t>
+        </is>
+      </c>
+      <c r="H540" t="n">
+        <v>122</v>
       </c>
       <c r="I540" s="2" t="n">
         <v>205940.46</v>
@@ -41564,15 +41694,28 @@
           <t>00004-00005885</t>
         </is>
       </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>Sin Clasificacion</t>
+          <t>Ambulatorio</t>
         </is>
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>GENERAL</t>
-        </is>
+          <t>OSSURRBAC</t>
+        </is>
+      </c>
+      <c r="H541" t="n">
+        <v>122</v>
       </c>
       <c r="I541" s="2" t="n">
         <v>99563.19</v>
@@ -41603,15 +41746,28 @@
           <t>00004-00005895</t>
         </is>
       </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>Sin Clasificacion</t>
+          <t>Ambulatorio</t>
         </is>
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>GENERAL</t>
-        </is>
+          <t>OSPLYFC</t>
+        </is>
+      </c>
+      <c r="H542" t="n">
+        <v>92</v>
       </c>
       <c r="I542" s="2" t="n">
         <v>362050.99</v>
@@ -41642,15 +41798,28 @@
           <t>00004-00005896</t>
         </is>
       </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>Sin Clasificacion</t>
+          <t>Ambulatorio</t>
         </is>
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>GENERAL</t>
-        </is>
+          <t>OSSURRBAC</t>
+        </is>
+      </c>
+      <c r="H543" t="n">
+        <v>92</v>
       </c>
       <c r="I543" s="2" t="n">
         <v>84248.37</v>
@@ -41681,15 +41850,28 @@
           <t>00004-00005900</t>
         </is>
       </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>Sin Clasificacion</t>
+          <t>Internado</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>GENERAL</t>
-        </is>
+          <t>OSPIF</t>
+        </is>
+      </c>
+      <c r="H544" t="n">
+        <v>92</v>
       </c>
       <c r="I544" s="2" t="n">
         <v>233927.12</v>
@@ -41698,7 +41880,7 @@
         <v>0</v>
       </c>
       <c r="K544" s="2" t="n">
-        <v>0</v>
+        <v>91155.10000000001</v>
       </c>
       <c r="L544" s="2" t="n">
         <v>142772.02</v>
@@ -41720,15 +41902,28 @@
           <t>00004-00005925</t>
         </is>
       </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>Sin Clasificacion</t>
+          <t>Internado</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>GENERAL</t>
-        </is>
+          <t>OSSURRBAC</t>
+        </is>
+      </c>
+      <c r="H545" t="n">
+        <v>61</v>
       </c>
       <c r="I545" s="2" t="n">
         <v>755673.61</v>
@@ -55000,7 +55195,7 @@
         <v>0</v>
       </c>
       <c r="L800" s="2" t="n">
-        <v>0</v>
+        <v>115832.78</v>
       </c>
     </row>
     <row r="801">
@@ -55052,7 +55247,7 @@
         <v>0</v>
       </c>
       <c r="L801" s="2" t="n">
-        <v>0</v>
+        <v>649361.9399999999</v>
       </c>
     </row>
     <row r="802">
@@ -55104,7 +55299,7 @@
         <v>0</v>
       </c>
       <c r="L802" s="2" t="n">
-        <v>0</v>
+        <v>684325.78</v>
       </c>
     </row>
     <row r="803">
@@ -55156,7 +55351,7 @@
         <v>0</v>
       </c>
       <c r="L803" s="2" t="n">
-        <v>0</v>
+        <v>1453874.91</v>
       </c>
     </row>
     <row r="804">
@@ -55208,7 +55403,7 @@
         <v>0</v>
       </c>
       <c r="L804" s="2" t="n">
-        <v>0</v>
+        <v>571793.11</v>
       </c>
     </row>
     <row r="805">
@@ -58068,7 +58263,7 @@
         <v>0</v>
       </c>
       <c r="L859" s="2" t="n">
-        <v>1499370.08</v>
+        <v>3017142.8</v>
       </c>
     </row>
     <row r="860">
@@ -58120,7 +58315,7 @@
         <v>0</v>
       </c>
       <c r="L860" s="2" t="n">
-        <v>60267.42</v>
+        <v>1499370.08</v>
       </c>
     </row>
     <row r="861">
@@ -58172,7 +58367,7 @@
         <v>0</v>
       </c>
       <c r="L861" s="2" t="n">
-        <v>21733</v>
+        <v>60267.42</v>
       </c>
     </row>
     <row r="862">
@@ -58224,7 +58419,7 @@
         <v>0</v>
       </c>
       <c r="L862" s="2" t="n">
-        <v>34045.3</v>
+        <v>21733</v>
       </c>
     </row>
     <row r="863">
@@ -58276,7 +58471,7 @@
         <v>0</v>
       </c>
       <c r="L863" s="2" t="n">
-        <v>392263.88</v>
+        <v>34045.3</v>
       </c>
     </row>
     <row r="864">
@@ -58328,7 +58523,7 @@
         <v>0</v>
       </c>
       <c r="L864" s="2" t="n">
-        <v>7664269.35</v>
+        <v>392263.88</v>
       </c>
     </row>
     <row r="865">
@@ -58380,7 +58575,7 @@
         <v>0</v>
       </c>
       <c r="L865" s="2" t="n">
-        <v>1365682.29</v>
+        <v>160910.1</v>
       </c>
     </row>
     <row r="866">
@@ -58432,7 +58627,7 @@
         <v>0</v>
       </c>
       <c r="L866" s="2" t="n">
-        <v>725680</v>
+        <v>7664269.35</v>
       </c>
     </row>
     <row r="867">
@@ -58484,7 +58679,7 @@
         <v>0</v>
       </c>
       <c r="L867" s="2" t="n">
-        <v>82184.34</v>
+        <v>1365682.29</v>
       </c>
     </row>
     <row r="868">
@@ -58536,7 +58731,7 @@
         <v>0</v>
       </c>
       <c r="L868" s="2" t="n">
-        <v>101976.5</v>
+        <v>725680</v>
       </c>
     </row>
     <row r="869">
@@ -58588,7 +58783,7 @@
         <v>0</v>
       </c>
       <c r="L869" s="2" t="n">
-        <v>17983.88</v>
+        <v>82184.34</v>
       </c>
     </row>
     <row r="870">
@@ -58640,7 +58835,7 @@
         <v>0</v>
       </c>
       <c r="L870" s="2" t="n">
-        <v>18105.6</v>
+        <v>101976.5</v>
       </c>
     </row>
     <row r="871">
@@ -58692,7 +58887,7 @@
         <v>0</v>
       </c>
       <c r="L871" s="2" t="n">
-        <v>21059.44</v>
+        <v>17983.88</v>
       </c>
     </row>
     <row r="872">
@@ -58744,7 +58939,7 @@
         <v>0</v>
       </c>
       <c r="L872" s="2" t="n">
-        <v>2850705.51</v>
+        <v>18105.6</v>
       </c>
     </row>
     <row r="873">
@@ -58796,7 +58991,7 @@
         <v>0</v>
       </c>
       <c r="L873" s="2" t="n">
-        <v>1053353.71</v>
+        <v>21059.44</v>
       </c>
     </row>
     <row r="874">
@@ -58848,7 +59043,7 @@
         <v>0</v>
       </c>
       <c r="L874" s="2" t="n">
-        <v>158885.19</v>
+        <v>2850705.51</v>
       </c>
     </row>
     <row r="875">
@@ -58900,7 +59095,7 @@
         <v>0</v>
       </c>
       <c r="L875" s="2" t="n">
-        <v>2303237.09</v>
+        <v>1053353.71</v>
       </c>
     </row>
     <row r="876">
@@ -58952,7 +59147,7 @@
         <v>0</v>
       </c>
       <c r="L876" s="2" t="n">
-        <v>2998785.71</v>
+        <v>158885.19</v>
       </c>
     </row>
     <row r="877">
@@ -59004,7 +59199,7 @@
         <v>0</v>
       </c>
       <c r="L877" s="2" t="n">
-        <v>2425500</v>
+        <v>2303237.09</v>
       </c>
     </row>
     <row r="878">
@@ -59056,7 +59251,7 @@
         <v>0</v>
       </c>
       <c r="L878" s="2" t="n">
-        <v>2940000</v>
+        <v>2998785.71</v>
       </c>
     </row>
     <row r="879">
@@ -59108,7 +59303,7 @@
         <v>0</v>
       </c>
       <c r="L879" s="2" t="n">
-        <v>215775</v>
+        <v>2425500</v>
       </c>
     </row>
     <row r="880">
@@ -59160,7 +59355,7 @@
         <v>0</v>
       </c>
       <c r="L880" s="2" t="n">
-        <v>981925</v>
+        <v>2940000</v>
       </c>
     </row>
     <row r="881">
@@ -59212,7 +59407,7 @@
         <v>0</v>
       </c>
       <c r="L881" s="2" t="n">
-        <v>205601.57</v>
+        <v>215775</v>
       </c>
     </row>
     <row r="882">
@@ -59264,7 +59459,7 @@
         <v>0</v>
       </c>
       <c r="L882" s="2" t="n">
-        <v>26094.56</v>
+        <v>981925</v>
       </c>
     </row>
     <row r="883">
@@ -59316,7 +59511,7 @@
         <v>0</v>
       </c>
       <c r="L883" s="2" t="n">
-        <v>60850</v>
+        <v>205601.57</v>
       </c>
     </row>
     <row r="884">
@@ -59368,7 +59563,7 @@
         <v>0</v>
       </c>
       <c r="L884" s="2" t="n">
-        <v>56688.28</v>
+        <v>26094.56</v>
       </c>
     </row>
     <row r="885">
@@ -59420,7 +59615,7 @@
         <v>0</v>
       </c>
       <c r="L885" s="2" t="n">
-        <v>23262.96</v>
+        <v>60850</v>
       </c>
     </row>
     <row r="886">
@@ -59472,7 +59667,7 @@
         <v>0</v>
       </c>
       <c r="L886" s="2" t="n">
-        <v>497747.32</v>
+        <v>56688.28</v>
       </c>
     </row>
     <row r="887">
@@ -59524,7 +59719,7 @@
         <v>0</v>
       </c>
       <c r="L887" s="2" t="n">
-        <v>17700.06</v>
+        <v>23262.96</v>
       </c>
     </row>
     <row r="888">
@@ -59576,7 +59771,7 @@
         <v>0</v>
       </c>
       <c r="L888" s="2" t="n">
-        <v>423000</v>
+        <v>497747.32</v>
       </c>
     </row>
     <row r="889">
@@ -59628,7 +59823,7 @@
         <v>0</v>
       </c>
       <c r="L889" s="2" t="n">
-        <v>457115.8</v>
+        <v>17700.06</v>
       </c>
     </row>
     <row r="890">
@@ -59680,7 +59875,7 @@
         <v>0</v>
       </c>
       <c r="L890" s="2" t="n">
-        <v>413195.46</v>
+        <v>423000</v>
       </c>
     </row>
     <row r="891">
@@ -59732,7 +59927,7 @@
         <v>0</v>
       </c>
       <c r="L891" s="2" t="n">
-        <v>53488.34</v>
+        <v>457115.8</v>
       </c>
     </row>
     <row r="892">
@@ -59784,7 +59979,7 @@
         <v>0</v>
       </c>
       <c r="L892" s="2" t="n">
-        <v>78624</v>
+        <v>413195.46</v>
       </c>
     </row>
     <row r="893">
@@ -59836,7 +60031,7 @@
         <v>0</v>
       </c>
       <c r="L893" s="2" t="n">
-        <v>20945.33</v>
+        <v>53488.34</v>
       </c>
     </row>
     <row r="894">
@@ -59888,7 +60083,7 @@
         <v>0</v>
       </c>
       <c r="L894" s="2" t="n">
-        <v>267595.91</v>
+        <v>78624</v>
       </c>
     </row>
     <row r="895">
@@ -59940,7 +60135,7 @@
         <v>0</v>
       </c>
       <c r="L895" s="2" t="n">
-        <v>718992.42</v>
+        <v>20945.33</v>
       </c>
     </row>
     <row r="896">
@@ -59992,7 +60187,7 @@
         <v>0</v>
       </c>
       <c r="L896" s="2" t="n">
-        <v>78412.84</v>
+        <v>267595.91</v>
       </c>
     </row>
     <row r="897">
@@ -60044,7 +60239,7 @@
         <v>0</v>
       </c>
       <c r="L897" s="2" t="n">
-        <v>149262.05</v>
+        <v>718992.42</v>
       </c>
     </row>
     <row r="898">
@@ -60096,7 +60291,7 @@
         <v>0</v>
       </c>
       <c r="L898" s="2" t="n">
-        <v>91850.56</v>
+        <v>78412.84</v>
       </c>
     </row>
     <row r="899">
@@ -60148,7 +60343,7 @@
         <v>0</v>
       </c>
       <c r="L899" s="2" t="n">
-        <v>171810.37</v>
+        <v>149262.05</v>
       </c>
     </row>
     <row r="900">
@@ -60200,7 +60395,7 @@
         <v>0</v>
       </c>
       <c r="L900" s="2" t="n">
-        <v>65717.86</v>
+        <v>91850.56</v>
       </c>
     </row>
     <row r="901">
@@ -60252,7 +60447,7 @@
         <v>0</v>
       </c>
       <c r="L901" s="2" t="n">
-        <v>38125.92</v>
+        <v>171810.37</v>
       </c>
     </row>
     <row r="902">
@@ -60304,7 +60499,7 @@
         <v>0</v>
       </c>
       <c r="L902" s="2" t="n">
-        <v>87524.03999999999</v>
+        <v>65717.86</v>
       </c>
     </row>
     <row r="903">
@@ -60356,7 +60551,7 @@
         <v>0</v>
       </c>
       <c r="L903" s="2" t="n">
-        <v>204000</v>
+        <v>38125.92</v>
       </c>
     </row>
     <row r="904">
@@ -60408,7 +60603,7 @@
         <v>0</v>
       </c>
       <c r="L904" s="2" t="n">
-        <v>39467</v>
+        <v>87524.03999999999</v>
       </c>
     </row>
     <row r="905">
@@ -60460,7 +60655,7 @@
         <v>0</v>
       </c>
       <c r="L905" s="2" t="n">
-        <v>3076639.9</v>
+        <v>204000</v>
       </c>
     </row>
     <row r="906">
@@ -60512,7 +60707,7 @@
         <v>0</v>
       </c>
       <c r="L906" s="2" t="n">
-        <v>4392027.4</v>
+        <v>39467</v>
       </c>
     </row>
     <row r="907">
@@ -60564,7 +60759,7 @@
         <v>0</v>
       </c>
       <c r="L907" s="2" t="n">
-        <v>3996654.02</v>
+        <v>3076639.9</v>
       </c>
     </row>
     <row r="908">
@@ -60616,7 +60811,7 @@
         <v>0</v>
       </c>
       <c r="L908" s="2" t="n">
-        <v>825000</v>
+        <v>4392027.4</v>
       </c>
     </row>
     <row r="909">
@@ -60668,7 +60863,7 @@
         <v>0</v>
       </c>
       <c r="L909" s="2" t="n">
-        <v>327208</v>
+        <v>3996654.02</v>
       </c>
     </row>
     <row r="910">
@@ -60720,7 +60915,7 @@
         <v>0</v>
       </c>
       <c r="L910" s="2" t="n">
-        <v>260629</v>
+        <v>825000</v>
       </c>
     </row>
     <row r="911">
@@ -60772,7 +60967,7 @@
         <v>0</v>
       </c>
       <c r="L911" s="2" t="n">
-        <v>17862</v>
+        <v>327208</v>
       </c>
     </row>
     <row r="912">
@@ -60824,7 +61019,7 @@
         <v>0</v>
       </c>
       <c r="L912" s="2" t="n">
-        <v>76769</v>
+        <v>260629</v>
       </c>
     </row>
     <row r="913">
@@ -60876,7 +61071,7 @@
         <v>0</v>
       </c>
       <c r="L913" s="2" t="n">
-        <v>245598.2</v>
+        <v>17862</v>
       </c>
     </row>
     <row r="914">
@@ -60928,7 +61123,7 @@
         <v>0</v>
       </c>
       <c r="L914" s="2" t="n">
-        <v>528390.64</v>
+        <v>76769</v>
       </c>
     </row>
     <row r="915">
@@ -60980,7 +61175,7 @@
         <v>0</v>
       </c>
       <c r="L915" s="2" t="n">
-        <v>933853.5</v>
+        <v>245598.2</v>
       </c>
     </row>
     <row r="916">
@@ -61032,7 +61227,7 @@
         <v>0</v>
       </c>
       <c r="L916" s="2" t="n">
-        <v>1632036</v>
+        <v>528390.64</v>
       </c>
     </row>
     <row r="917">
@@ -61084,7 +61279,7 @@
         <v>0</v>
       </c>
       <c r="L917" s="2" t="n">
-        <v>60000</v>
+        <v>933853.5</v>
       </c>
     </row>
     <row r="918">
@@ -61136,7 +61331,7 @@
         <v>0</v>
       </c>
       <c r="L918" s="2" t="n">
-        <v>60000</v>
+        <v>1632036</v>
       </c>
     </row>
     <row r="919">
@@ -61188,7 +61383,7 @@
         <v>0</v>
       </c>
       <c r="L919" s="2" t="n">
-        <v>600000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="920">
@@ -61240,7 +61435,7 @@
         <v>0</v>
       </c>
       <c r="L920" s="2" t="n">
-        <v>27370</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="921">
@@ -61292,7 +61487,7 @@
         <v>0</v>
       </c>
       <c r="L921" s="2" t="n">
-        <v>188789.6</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="922">
@@ -61344,7 +61539,7 @@
         <v>0</v>
       </c>
       <c r="L922" s="2" t="n">
-        <v>1042650.99</v>
+        <v>27370</v>
       </c>
     </row>
     <row r="923">
@@ -61396,7 +61591,7 @@
         <v>0</v>
       </c>
       <c r="L923" s="2" t="n">
-        <v>21000</v>
+        <v>188789.6</v>
       </c>
     </row>
     <row r="924">
@@ -61448,7 +61643,7 @@
         <v>0</v>
       </c>
       <c r="L924" s="2" t="n">
-        <v>441000</v>
+        <v>1042650.99</v>
       </c>
     </row>
     <row r="925">
@@ -61500,7 +61695,7 @@
         <v>0</v>
       </c>
       <c r="L925" s="2" t="n">
-        <v>433925</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="926">
@@ -61552,7 +61747,7 @@
         <v>0</v>
       </c>
       <c r="L926" s="2" t="n">
-        <v>733125</v>
+        <v>441000</v>
       </c>
     </row>
     <row r="927">
@@ -61604,7 +61799,7 @@
         <v>0</v>
       </c>
       <c r="L927" s="2" t="n">
-        <v>51536</v>
+        <v>433925</v>
       </c>
     </row>
     <row r="928">
@@ -61656,7 +61851,7 @@
         <v>0</v>
       </c>
       <c r="L928" s="2" t="n">
-        <v>368144</v>
+        <v>733125</v>
       </c>
     </row>
     <row r="929">
@@ -61708,7 +61903,7 @@
         <v>0</v>
       </c>
       <c r="L929" s="2" t="n">
-        <v>186000</v>
+        <v>51536</v>
       </c>
     </row>
     <row r="930">
@@ -61760,7 +61955,7 @@
         <v>0</v>
       </c>
       <c r="L930" s="2" t="n">
-        <v>216720</v>
+        <v>368144</v>
       </c>
     </row>
     <row r="931">
@@ -61812,7 +62007,7 @@
         <v>0</v>
       </c>
       <c r="L931" s="2" t="n">
-        <v>319391.94</v>
+        <v>186000</v>
       </c>
     </row>
     <row r="932">
@@ -61864,7 +62059,7 @@
         <v>0</v>
       </c>
       <c r="L932" s="2" t="n">
-        <v>1132791.13</v>
+        <v>216720</v>
       </c>
     </row>
     <row r="933">
@@ -61916,7 +62111,7 @@
         <v>0</v>
       </c>
       <c r="L933" s="2" t="n">
-        <v>272384.5</v>
+        <v>319391.94</v>
       </c>
     </row>
     <row r="934">
@@ -61968,7 +62163,7 @@
         <v>0</v>
       </c>
       <c r="L934" s="2" t="n">
-        <v>136849.56</v>
+        <v>1132791.13</v>
       </c>
     </row>
     <row r="935">
@@ -62012,7 +62207,7 @@
         <v>0</v>
       </c>
       <c r="L935" s="2" t="n">
-        <v>68415.8</v>
+        <v>272384.5</v>
       </c>
     </row>
     <row r="936">
@@ -62056,7 +62251,7 @@
         <v>0</v>
       </c>
       <c r="L936" s="2" t="n">
-        <v>104313.98</v>
+        <v>136849.56</v>
       </c>
     </row>
     <row r="937">
@@ -62100,7 +62295,7 @@
         <v>0</v>
       </c>
       <c r="L937" s="2" t="n">
-        <v>218317.18</v>
+        <v>68415.8</v>
       </c>
     </row>
     <row r="938">
@@ -62144,7 +62339,7 @@
         <v>0</v>
       </c>
       <c r="L938" s="2" t="n">
-        <v>152335.33</v>
+        <v>104313.98</v>
       </c>
     </row>
     <row r="939">
@@ -62188,7 +62383,7 @@
         <v>0</v>
       </c>
       <c r="L939" s="2" t="n">
-        <v>80584.78</v>
+        <v>218317.18</v>
       </c>
     </row>
     <row r="940">
@@ -62232,7 +62427,7 @@
         <v>0</v>
       </c>
       <c r="L940" s="2" t="n">
-        <v>152280</v>
+        <v>152335.33</v>
       </c>
     </row>
     <row r="941">
@@ -62276,7 +62471,7 @@
         <v>0</v>
       </c>
       <c r="L941" s="2" t="n">
-        <v>91830.77</v>
+        <v>80584.78</v>
       </c>
     </row>
     <row r="942">
@@ -62320,7 +62515,7 @@
         <v>0</v>
       </c>
       <c r="L942" s="2" t="n">
-        <v>1116342.21</v>
+        <v>152280</v>
       </c>
     </row>
     <row r="943">
@@ -62364,7 +62559,7 @@
         <v>0</v>
       </c>
       <c r="L943" s="2" t="n">
-        <v>215374.55</v>
+        <v>91830.77</v>
       </c>
     </row>
     <row r="944">
@@ -62408,7 +62603,7 @@
         <v>0</v>
       </c>
       <c r="L944" s="2" t="n">
-        <v>51290</v>
+        <v>1116342.21</v>
       </c>
     </row>
     <row r="945">
@@ -62452,7 +62647,7 @@
         <v>0</v>
       </c>
       <c r="L945" s="2" t="n">
-        <v>33583.4</v>
+        <v>215374.55</v>
       </c>
     </row>
     <row r="946">
@@ -62496,7 +62691,7 @@
         <v>0</v>
       </c>
       <c r="L946" s="2" t="n">
-        <v>16023.4</v>
+        <v>51290</v>
       </c>
     </row>
     <row r="947">
@@ -62540,7 +62735,7 @@
         <v>0</v>
       </c>
       <c r="L947" s="2" t="n">
-        <v>108536.3</v>
+        <v>33583.4</v>
       </c>
     </row>
     <row r="948">
@@ -62584,7 +62779,7 @@
         <v>0</v>
       </c>
       <c r="L948" s="2" t="n">
-        <v>114254.91</v>
+        <v>16023.4</v>
       </c>
     </row>
     <row r="949">
@@ -62628,7 +62823,7 @@
         <v>0</v>
       </c>
       <c r="L949" s="2" t="n">
-        <v>26780</v>
+        <v>108536.3</v>
       </c>
     </row>
     <row r="950">
@@ -62672,7 +62867,7 @@
         <v>0</v>
       </c>
       <c r="L950" s="2" t="n">
-        <v>49468.56</v>
+        <v>114254.91</v>
       </c>
     </row>
     <row r="951">
@@ -62716,7 +62911,7 @@
         <v>0</v>
       </c>
       <c r="L951" s="2" t="n">
-        <v>727697.12</v>
+        <v>26780</v>
       </c>
     </row>
     <row r="952">
@@ -62760,7 +62955,7 @@
         <v>0</v>
       </c>
       <c r="L952" s="2" t="n">
-        <v>347025.72</v>
+        <v>49468.56</v>
       </c>
     </row>
     <row r="953">
@@ -62804,7 +62999,7 @@
         <v>0</v>
       </c>
       <c r="L953" s="2" t="n">
-        <v>71729.92</v>
+        <v>727697.12</v>
       </c>
     </row>
     <row r="954">
@@ -62848,7 +63043,7 @@
         <v>0</v>
       </c>
       <c r="L954" s="2" t="n">
-        <v>46184.4</v>
+        <v>347025.72</v>
       </c>
     </row>
     <row r="955">
@@ -62892,7 +63087,7 @@
         <v>0</v>
       </c>
       <c r="L955" s="2" t="n">
-        <v>169830.35</v>
+        <v>71729.92</v>
       </c>
     </row>
     <row r="956">
@@ -62936,7 +63131,7 @@
         <v>0</v>
       </c>
       <c r="L956" s="2" t="n">
-        <v>11504.02</v>
+        <v>46184.4</v>
       </c>
     </row>
     <row r="957">
@@ -62980,7 +63175,7 @@
         <v>0</v>
       </c>
       <c r="L957" s="2" t="n">
-        <v>152.01</v>
+        <v>169830.35</v>
       </c>
     </row>
     <row r="958">
@@ -63024,7 +63219,7 @@
         <v>0</v>
       </c>
       <c r="L958" s="2" t="n">
-        <v>6371.47</v>
+        <v>11504.02</v>
       </c>
     </row>
     <row r="959">
@@ -63068,7 +63263,7 @@
         <v>0</v>
       </c>
       <c r="L959" s="2" t="n">
-        <v>11199</v>
+        <v>152.01</v>
       </c>
     </row>
     <row r="960">
@@ -63112,7 +63307,7 @@
         <v>0</v>
       </c>
       <c r="L960" s="2" t="n">
-        <v>37512</v>
+        <v>6371.47</v>
       </c>
     </row>
     <row r="961">
@@ -63156,7 +63351,7 @@
         <v>0</v>
       </c>
       <c r="L961" s="2" t="n">
-        <v>65491</v>
+        <v>11199</v>
       </c>
     </row>
     <row r="962">
@@ -63200,7 +63395,7 @@
         <v>0</v>
       </c>
       <c r="L962" s="2" t="n">
-        <v>237256</v>
+        <v>37512</v>
       </c>
     </row>
     <row r="963">
@@ -63244,7 +63439,7 @@
         <v>0</v>
       </c>
       <c r="L963" s="2" t="n">
-        <v>527658</v>
+        <v>65491</v>
       </c>
     </row>
     <row r="964">
@@ -63288,7 +63483,7 @@
         <v>0</v>
       </c>
       <c r="L964" s="2" t="n">
-        <v>276133</v>
+        <v>237256</v>
       </c>
     </row>
     <row r="965">
@@ -63332,7 +63527,7 @@
         <v>0</v>
       </c>
       <c r="L965" s="2" t="n">
-        <v>24768</v>
+        <v>527658</v>
       </c>
     </row>
     <row r="966">
@@ -63376,7 +63571,7 @@
         <v>0</v>
       </c>
       <c r="L966" s="2" t="n">
-        <v>320650</v>
+        <v>276133</v>
       </c>
     </row>
     <row r="967">
@@ -63420,7 +63615,7 @@
         <v>0</v>
       </c>
       <c r="L967" s="2" t="n">
-        <v>1292379.75</v>
+        <v>24768</v>
       </c>
     </row>
     <row r="968">
@@ -63464,7 +63659,7 @@
         <v>0</v>
       </c>
       <c r="L968" s="2" t="n">
-        <v>1287167.43</v>
+        <v>320650</v>
       </c>
     </row>
     <row r="969">
@@ -63508,7 +63703,7 @@
         <v>0</v>
       </c>
       <c r="L969" s="2" t="n">
-        <v>70415.36</v>
+        <v>1292379.75</v>
       </c>
     </row>
     <row r="970">
@@ -63552,7 +63747,7 @@
         <v>0</v>
       </c>
       <c r="L970" s="2" t="n">
-        <v>69897.60000000001</v>
+        <v>1287167.43</v>
       </c>
     </row>
     <row r="971">
@@ -63604,7 +63799,7 @@
         <v>0</v>
       </c>
       <c r="L971" s="2" t="n">
-        <v>62131.2</v>
+        <v>70415.36</v>
       </c>
     </row>
     <row r="972">
@@ -63656,7 +63851,7 @@
         <v>0</v>
       </c>
       <c r="L972" s="2" t="n">
-        <v>165000</v>
+        <v>69897.60000000001</v>
       </c>
     </row>
     <row r="973">
@@ -63708,7 +63903,7 @@
         <v>0</v>
       </c>
       <c r="L973" s="2" t="n">
-        <v>160000</v>
+        <v>62131.2</v>
       </c>
     </row>
     <row r="974">
@@ -63760,7 +63955,7 @@
         <v>0</v>
       </c>
       <c r="L974" s="2" t="n">
-        <v>795000</v>
+        <v>165000</v>
       </c>
     </row>
     <row r="975">
@@ -63812,7 +64007,7 @@
         <v>0</v>
       </c>
       <c r="L975" s="2" t="n">
-        <v>120000</v>
+        <v>160000</v>
       </c>
     </row>
     <row r="976">
@@ -63864,7 +64059,7 @@
         <v>0</v>
       </c>
       <c r="L976" s="2" t="n">
-        <v>858000</v>
+        <v>795000</v>
       </c>
     </row>
     <row r="977">
@@ -63916,7 +64111,7 @@
         <v>0</v>
       </c>
       <c r="L977" s="2" t="n">
-        <v>1067000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="978">
@@ -63968,7 +64163,7 @@
         <v>0</v>
       </c>
       <c r="L978" s="2" t="n">
-        <v>200000</v>
+        <v>858000</v>
       </c>
     </row>
     <row r="979">
@@ -64020,7 +64215,7 @@
         <v>0</v>
       </c>
       <c r="L979" s="2" t="n">
-        <v>25300</v>
+        <v>1067000</v>
       </c>
     </row>
     <row r="980">
@@ -64072,7 +64267,7 @@
         <v>0</v>
       </c>
       <c r="L980" s="2" t="n">
-        <v>486457.8</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="981">
@@ -64124,7 +64319,7 @@
         <v>0</v>
       </c>
       <c r="L981" s="2" t="n">
-        <v>475500</v>
+        <v>25300</v>
       </c>
     </row>
     <row r="982">
@@ -64176,7 +64371,7 @@
         <v>0</v>
       </c>
       <c r="L982" s="2" t="n">
-        <v>90667.33</v>
+        <v>486457.8</v>
       </c>
     </row>
     <row r="983">
@@ -64228,7 +64423,7 @@
         <v>0</v>
       </c>
       <c r="L983" s="2" t="n">
-        <v>2021280.98</v>
+        <v>475500</v>
       </c>
     </row>
     <row r="984">
@@ -64280,7 +64475,7 @@
         <v>0</v>
       </c>
       <c r="L984" s="2" t="n">
-        <v>85884.33</v>
+        <v>90667.33</v>
       </c>
     </row>
     <row r="985">
@@ -64332,7 +64527,7 @@
         <v>0</v>
       </c>
       <c r="L985" s="2" t="n">
-        <v>3630000</v>
+        <v>2021280.98</v>
       </c>
     </row>
     <row r="986">
@@ -64384,7 +64579,7 @@
         <v>0</v>
       </c>
       <c r="L986" s="2" t="n">
-        <v>216000</v>
+        <v>85884.33</v>
       </c>
     </row>
     <row r="987">
@@ -64436,7 +64631,7 @@
         <v>0</v>
       </c>
       <c r="L987" s="2" t="n">
-        <v>83094.35000000001</v>
+        <v>3630000</v>
       </c>
     </row>
     <row r="988">
@@ -64488,7 +64683,7 @@
         <v>0</v>
       </c>
       <c r="L988" s="2" t="n">
-        <v>244925.7</v>
+        <v>216000</v>
       </c>
     </row>
     <row r="989">
@@ -64540,7 +64735,7 @@
         <v>0</v>
       </c>
       <c r="L989" s="2" t="n">
-        <v>951358.6899999999</v>
+        <v>142623</v>
       </c>
     </row>
     <row r="990">
@@ -64592,7 +64787,7 @@
         <v>0</v>
       </c>
       <c r="L990" s="2" t="n">
-        <v>9705.6</v>
+        <v>213934.5</v>
       </c>
     </row>
     <row r="991">
@@ -64644,7 +64839,7 @@
         <v>0</v>
       </c>
       <c r="L991" s="2" t="n">
-        <v>780862.08</v>
+        <v>83094.35000000001</v>
       </c>
     </row>
     <row r="992">
@@ -64696,7 +64891,7 @@
         <v>0</v>
       </c>
       <c r="L992" s="2" t="n">
-        <v>508186.56</v>
+        <v>244925.7</v>
       </c>
     </row>
     <row r="993">
@@ -64748,7 +64943,7 @@
         <v>0</v>
       </c>
       <c r="L993" s="2" t="n">
-        <v>419639.94</v>
+        <v>951358.6899999999</v>
       </c>
     </row>
     <row r="994">
@@ -64800,7 +64995,7 @@
         <v>0</v>
       </c>
       <c r="L994" s="2" t="n">
-        <v>440000</v>
+        <v>9705.6</v>
       </c>
     </row>
     <row r="995">
@@ -64852,7 +65047,7 @@
         <v>0</v>
       </c>
       <c r="L995" s="2" t="n">
-        <v>21864.78</v>
+        <v>780862.08</v>
       </c>
     </row>
     <row r="996">
@@ -64904,7 +65099,7 @@
         <v>0</v>
       </c>
       <c r="L996" s="2" t="n">
-        <v>909000</v>
+        <v>508186.56</v>
       </c>
     </row>
     <row r="997">
@@ -64956,7 +65151,7 @@
         <v>0</v>
       </c>
       <c r="L997" s="2" t="n">
-        <v>1771000</v>
+        <v>419639.94</v>
       </c>
     </row>
     <row r="998">
@@ -65008,7 +65203,7 @@
         <v>0</v>
       </c>
       <c r="L998" s="2" t="n">
-        <v>60678</v>
+        <v>440000</v>
       </c>
     </row>
     <row r="999">
@@ -65060,7 +65255,7 @@
         <v>0</v>
       </c>
       <c r="L999" s="2" t="n">
-        <v>89301</v>
+        <v>21864.78</v>
       </c>
     </row>
     <row r="1000">
@@ -65112,7 +65307,7 @@
         <v>0</v>
       </c>
       <c r="L1000" s="2" t="n">
-        <v>761962</v>
+        <v>909000</v>
       </c>
     </row>
     <row r="1001">
@@ -65164,7 +65359,7 @@
         <v>0</v>
       </c>
       <c r="L1001" s="2" t="n">
-        <v>7800446.33</v>
+        <v>1771000</v>
       </c>
     </row>
     <row r="1002">
@@ -65216,7 +65411,7 @@
         <v>0</v>
       </c>
       <c r="L1002" s="2" t="n">
-        <v>1158847.62</v>
+        <v>60678</v>
       </c>
     </row>
     <row r="1003">
@@ -65268,7 +65463,7 @@
         <v>0</v>
       </c>
       <c r="L1003" s="2" t="n">
-        <v>2080692.61</v>
+        <v>89301</v>
       </c>
     </row>
     <row r="1004">
@@ -65320,7 +65515,7 @@
         <v>0</v>
       </c>
       <c r="L1004" s="2" t="n">
-        <v>2098721.11</v>
+        <v>761962</v>
       </c>
     </row>
     <row r="1005">
@@ -65372,7 +65567,7 @@
         <v>0</v>
       </c>
       <c r="L1005" s="2" t="n">
-        <v>27625.66</v>
+        <v>7800446.33</v>
       </c>
     </row>
     <row r="1006">
@@ -65424,7 +65619,7 @@
         <v>0</v>
       </c>
       <c r="L1006" s="2" t="n">
-        <v>519353.14</v>
+        <v>1158847.62</v>
       </c>
     </row>
     <row r="1007">
@@ -65476,7 +65671,7 @@
         <v>0</v>
       </c>
       <c r="L1007" s="2" t="n">
-        <v>30640</v>
+        <v>2080692.61</v>
       </c>
     </row>
     <row r="1008">
@@ -65528,7 +65723,7 @@
         <v>0</v>
       </c>
       <c r="L1008" s="2" t="n">
-        <v>77495.87</v>
+        <v>2098721.11</v>
       </c>
     </row>
     <row r="1009">
@@ -65580,7 +65775,7 @@
         <v>0</v>
       </c>
       <c r="L1009" s="2" t="n">
-        <v>774958.7</v>
+        <v>27625.66</v>
       </c>
     </row>
     <row r="1010">
@@ -65632,7 +65827,7 @@
         <v>0</v>
       </c>
       <c r="L1010" s="2" t="n">
-        <v>163500.39</v>
+        <v>519353.14</v>
       </c>
     </row>
     <row r="1011">
@@ -65684,7 +65879,7 @@
         <v>0</v>
       </c>
       <c r="L1011" s="2" t="n">
-        <v>1779717.61</v>
+        <v>30640</v>
       </c>
     </row>
     <row r="1012">
@@ -65736,7 +65931,7 @@
         <v>0</v>
       </c>
       <c r="L1012" s="2" t="n">
-        <v>453371.83</v>
+        <v>77495.87</v>
       </c>
     </row>
     <row r="1013">
@@ -65788,7 +65983,7 @@
         <v>0</v>
       </c>
       <c r="L1013" s="2" t="n">
-        <v>27483.47</v>
+        <v>774958.7</v>
       </c>
     </row>
     <row r="1014">
@@ -65840,7 +66035,7 @@
         <v>0</v>
       </c>
       <c r="L1014" s="2" t="n">
-        <v>442224.5</v>
+        <v>163500.39</v>
       </c>
     </row>
     <row r="1015">
@@ -65892,7 +66087,7 @@
         <v>0</v>
       </c>
       <c r="L1015" s="2" t="n">
-        <v>594222.41</v>
+        <v>1779717.61</v>
       </c>
     </row>
     <row r="1016">
@@ -65944,7 +66139,7 @@
         <v>0</v>
       </c>
       <c r="L1016" s="2" t="n">
-        <v>83316</v>
+        <v>453371.83</v>
       </c>
     </row>
     <row r="1017">
@@ -65996,7 +66191,7 @@
         <v>0</v>
       </c>
       <c r="L1017" s="2" t="n">
-        <v>2976818.05</v>
+        <v>27483.47</v>
       </c>
     </row>
     <row r="1018">
@@ -66048,7 +66243,7 @@
         <v>0</v>
       </c>
       <c r="L1018" s="2" t="n">
-        <v>20645230.11</v>
+        <v>442224.5</v>
       </c>
     </row>
     <row r="1019">
@@ -66100,7 +66295,7 @@
         <v>0</v>
       </c>
       <c r="L1019" s="2" t="n">
-        <v>3065538.44</v>
+        <v>594222.41</v>
       </c>
     </row>
     <row r="1020">
@@ -66152,7 +66347,7 @@
         <v>0</v>
       </c>
       <c r="L1020" s="2" t="n">
-        <v>2392436.15</v>
+        <v>83316</v>
       </c>
     </row>
     <row r="1021">
@@ -66204,7 +66399,7 @@
         <v>0</v>
       </c>
       <c r="L1021" s="2" t="n">
-        <v>3889601.55</v>
+        <v>260000</v>
       </c>
     </row>
     <row r="1022">
@@ -66256,7 +66451,7 @@
         <v>0</v>
       </c>
       <c r="L1022" s="2" t="n">
-        <v>392650</v>
+        <v>1973505.76</v>
       </c>
     </row>
     <row r="1023">
@@ -66308,7 +66503,7 @@
         <v>0</v>
       </c>
       <c r="L1023" s="2" t="n">
-        <v>68000</v>
+        <v>2976818.05</v>
       </c>
     </row>
     <row r="1024">
@@ -66360,7 +66555,7 @@
         <v>0</v>
       </c>
       <c r="L1024" s="2" t="n">
-        <v>5185000</v>
+        <v>20645230.11</v>
       </c>
     </row>
     <row r="1025">
@@ -66412,7 +66607,7 @@
         <v>0</v>
       </c>
       <c r="L1025" s="2" t="n">
-        <v>16638208.85</v>
+        <v>3065538.44</v>
       </c>
     </row>
     <row r="1026">
@@ -66464,7 +66659,7 @@
         <v>0</v>
       </c>
       <c r="L1026" s="2" t="n">
-        <v>952729.96</v>
+        <v>2392436.15</v>
       </c>
     </row>
     <row r="1027">
@@ -66516,7 +66711,7 @@
         <v>0</v>
       </c>
       <c r="L1027" s="2" t="n">
-        <v>276888.6</v>
+        <v>3889601.55</v>
       </c>
     </row>
     <row r="1028">
@@ -66568,7 +66763,7 @@
         <v>0</v>
       </c>
       <c r="L1028" s="2" t="n">
-        <v>187926.14</v>
+        <v>392650</v>
       </c>
     </row>
     <row r="1029">
@@ -66620,7 +66815,7 @@
         <v>0</v>
       </c>
       <c r="L1029" s="2" t="n">
-        <v>725065.77</v>
+        <v>68000</v>
       </c>
     </row>
     <row r="1030">
@@ -66672,7 +66867,7 @@
         <v>0</v>
       </c>
       <c r="L1030" s="2" t="n">
-        <v>5230519.21</v>
+        <v>5185000</v>
       </c>
     </row>
     <row r="1031">
@@ -66724,7 +66919,7 @@
         <v>0</v>
       </c>
       <c r="L1031" s="2" t="n">
-        <v>10391656.65</v>
+        <v>16638208.85</v>
       </c>
     </row>
     <row r="1032">
@@ -66776,7 +66971,7 @@
         <v>0</v>
       </c>
       <c r="L1032" s="2" t="n">
-        <v>324557.81</v>
+        <v>952729.96</v>
       </c>
     </row>
     <row r="1033">
@@ -66828,7 +67023,7 @@
         <v>0</v>
       </c>
       <c r="L1033" s="2" t="n">
-        <v>334475.69</v>
+        <v>276888.6</v>
       </c>
     </row>
     <row r="1034">
@@ -66880,7 +67075,7 @@
         <v>0</v>
       </c>
       <c r="L1034" s="2" t="n">
-        <v>470899.34</v>
+        <v>187926.14</v>
       </c>
     </row>
     <row r="1035">
@@ -66932,7 +67127,7 @@
         <v>0</v>
       </c>
       <c r="L1035" s="2" t="n">
-        <v>1640472</v>
+        <v>725065.77</v>
       </c>
     </row>
     <row r="1036">
@@ -66984,7 +67179,7 @@
         <v>0</v>
       </c>
       <c r="L1036" s="2" t="n">
-        <v>2150250</v>
+        <v>5230519.21</v>
       </c>
     </row>
     <row r="1037">
@@ -67036,7 +67231,7 @@
         <v>0</v>
       </c>
       <c r="L1037" s="2" t="n">
-        <v>2150250</v>
+        <v>10391656.65</v>
       </c>
     </row>
     <row r="1038">
@@ -67088,7 +67283,7 @@
         <v>0</v>
       </c>
       <c r="L1038" s="2" t="n">
-        <v>558000</v>
+        <v>324557.81</v>
       </c>
     </row>
     <row r="1039">
@@ -67140,7 +67335,7 @@
         <v>0</v>
       </c>
       <c r="L1039" s="2" t="n">
-        <v>104359.2</v>
+        <v>334475.69</v>
       </c>
     </row>
     <row r="1040">
@@ -67192,7 +67387,7 @@
         <v>0</v>
       </c>
       <c r="L1040" s="2" t="n">
-        <v>347600</v>
+        <v>470899.34</v>
       </c>
     </row>
     <row r="1041">
@@ -67244,7 +67439,7 @@
         <v>0</v>
       </c>
       <c r="L1041" s="2" t="n">
-        <v>987646</v>
+        <v>1640472</v>
       </c>
     </row>
     <row r="1042">
@@ -67296,7 +67491,7 @@
         <v>0</v>
       </c>
       <c r="L1042" s="2" t="n">
-        <v>244000</v>
+        <v>2150250</v>
       </c>
     </row>
     <row r="1043">
@@ -67348,7 +67543,7 @@
         <v>0</v>
       </c>
       <c r="L1043" s="2" t="n">
-        <v>0</v>
+        <v>2150250</v>
       </c>
     </row>
     <row r="1044">
@@ -67400,7 +67595,7 @@
         <v>0</v>
       </c>
       <c r="L1044" s="2" t="n">
-        <v>0</v>
+        <v>558000</v>
       </c>
     </row>
     <row r="1045">
@@ -67452,7 +67647,7 @@
         <v>0</v>
       </c>
       <c r="L1045" s="2" t="n">
-        <v>0</v>
+        <v>104359.2</v>
       </c>
     </row>
     <row r="1046">
@@ -67504,7 +67699,7 @@
         <v>0</v>
       </c>
       <c r="L1046" s="2" t="n">
-        <v>0</v>
+        <v>347600</v>
       </c>
     </row>
     <row r="1047">
@@ -67556,7 +67751,7 @@
         <v>0</v>
       </c>
       <c r="L1047" s="2" t="n">
-        <v>0</v>
+        <v>32000</v>
       </c>
     </row>
     <row r="1048">
@@ -67608,7 +67803,7 @@
         <v>0</v>
       </c>
       <c r="L1048" s="2" t="n">
-        <v>0</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="1049">
@@ -67660,7 +67855,7 @@
         <v>0</v>
       </c>
       <c r="L1049" s="2" t="n">
-        <v>0</v>
+        <v>987646</v>
       </c>
     </row>
     <row r="1050">
@@ -67712,7 +67907,7 @@
         <v>0</v>
       </c>
       <c r="L1050" s="2" t="n">
-        <v>0</v>
+        <v>244000</v>
       </c>
     </row>
   </sheetData>

--- a/estado_resultado/TABLERO_Resumen.xlsx
+++ b/estado_resultado/TABLERO_Resumen.xlsx
@@ -2455,22 +2455,22 @@
         <v>0.01647090690982071</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>6278069.4</v>
+        <v>6115790.4</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>1106330.304429901</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>-1331017.634429901</v>
+        <v>-1168738.634429901</v>
       </c>
       <c r="N37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>-1331017.634429901</v>
+        <v>-1168738.634429901</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>-0.2198799975019421</v>
+        <v>-0.1930720084929153</v>
       </c>
     </row>
     <row r="38">
@@ -2669,22 +2669,22 @@
         <v>1</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>241954407.27</v>
+        <v>241792128.27</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>67168754.61</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>58396495.85000001</v>
+        <v>58558774.85000001</v>
       </c>
       <c r="N41" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>58396495.85000001</v>
+        <v>58558774.85000001</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.1588935302418606</v>
+        <v>0.1593350821332678</v>
       </c>
     </row>
   </sheetData>
@@ -3422,10 +3422,10 @@
         <v>43</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>102684329.21</v>
+        <v>102522050.21</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>102684329.21</v>
+        <v>102522050.21</v>
       </c>
     </row>
     <row r="35">
@@ -17617,10 +17617,10 @@
         </is>
       </c>
       <c r="C402" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D402" s="2" t="n">
-        <v>21459105.32</v>
+        <v>21219330.52</v>
       </c>
       <c r="E402" s="2" t="n">
         <v>0</v>
@@ -17632,7 +17632,7 @@
         <v>0</v>
       </c>
       <c r="H402" s="2" t="n">
-        <v>21459105.32</v>
+        <v>21219330.52</v>
       </c>
       <c r="I402" t="inlineStr">
         <is>
@@ -17862,10 +17862,10 @@
         </is>
       </c>
       <c r="C409" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D409" s="2" t="n">
-        <v>7130260.82</v>
+        <v>7207756.62</v>
       </c>
       <c r="E409" s="2" t="n">
         <v>0</v>
@@ -17877,7 +17877,7 @@
         <v>0</v>
       </c>
       <c r="H409" s="2" t="n">
-        <v>7130260.82</v>
+        <v>7207756.62</v>
       </c>
       <c r="I409" t="inlineStr">
         <is>
@@ -72412,7 +72412,7 @@
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t>CAMARA DE ENTIDADES DE SALUD - CES</t>
+          <t>SANATORIO DEL SALVADOR PRIVADO SA</t>
         </is>
       </c>
       <c r="C1065" t="inlineStr">
@@ -72444,7 +72444,7 @@
         <v>39</v>
       </c>
       <c r="I1065" s="2" t="n">
-        <v>239774.8</v>
+        <v>77495.8</v>
       </c>
       <c r="J1065" s="2" t="n">
         <v>0</v>
@@ -72453,7 +72453,7 @@
         <v>0</v>
       </c>
       <c r="L1065" s="2" t="n">
-        <v>239774.8</v>
+        <v>77495.8</v>
       </c>
     </row>
     <row r="1066">

--- a/estado_resultado/TABLERO_Resumen.xlsx
+++ b/estado_resultado/TABLERO_Resumen.xlsx
@@ -444,7 +444,7 @@
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
@@ -1860,25 +1860,25 @@
         <v>193070963.46</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.5164156772140958</v>
+        <v>0.5182817004005844</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>220822555.04</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>33325361.19763434</v>
+        <v>33445779.49521269</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-61076952.77763432</v>
+        <v>-61197371.07521267</v>
       </c>
       <c r="N26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>-61076952.77763432</v>
+        <v>-61197371.07521267</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-0.3163445796461678</v>
+        <v>-0.3169682793233246</v>
       </c>
     </row>
     <row r="27">
@@ -1914,25 +1914,25 @@
         <v>125495352.53</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.3356681206878028</v>
+        <v>0.336881028281057</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>106763986.2</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>21661351.22930155</v>
+        <v>21739622.64015919</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>-2929984.899301548</v>
+        <v>-3008256.310159188</v>
       </c>
       <c r="N27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>-2929984.899301548</v>
+        <v>-3008256.310159188</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.02334735781232318</v>
+        <v>-0.02397105748947999</v>
       </c>
     </row>
     <row r="28">
@@ -1968,25 +1968,25 @@
         <v>20442924.55</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.05467961901952231</v>
+        <v>0.05487719907260907</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>8942130.01</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>3528587.79153438</v>
+        <v>3541338.036976356</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>7972206.748465621</v>
+        <v>7959456.503023645</v>
       </c>
       <c r="N28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>7972206.748465621</v>
+        <v>7959456.503023645</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.3899738870026608</v>
+        <v>0.389350187325504</v>
       </c>
     </row>
     <row r="29">
@@ -2016,31 +2016,31 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>6053382.07</v>
+        <v>4707308.78</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>6053382.07</v>
+        <v>4707308.78</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.01619125602883504</v>
+        <v>0.0126363485999512</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>1045103.78</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>1044854.908966296</v>
+        <v>815449.4526276949</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3963423.381033704</v>
+        <v>2846755.547372305</v>
       </c>
       <c r="N29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>3963423.381033704</v>
+        <v>2846755.547372305</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.6547452870480557</v>
+        <v>0.6047522438866448</v>
       </c>
     </row>
     <row r="30">
@@ -2076,25 +2076,25 @@
         <v>15636658.92</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.04182408198947323</v>
+        <v>0.04197520967631455</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>2466796.4</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>2698993.660645251</v>
+        <v>2708746.239765466</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>10470868.85935475</v>
+        <v>10461116.28023453</v>
       </c>
       <c r="N30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>10470868.85935475</v>
+        <v>10461116.28023453</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>0.6696359441569727</v>
+        <v>0.6690122444798159</v>
       </c>
     </row>
     <row r="31">
@@ -2130,25 +2130,25 @@
         <v>5793567.12</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.01549631717863143</v>
+        <v>0.01555231177452848</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>1000009.081825183</v>
+        <v>1003622.527767514</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>4793558.038174816</v>
+        <v>4789944.592232486</v>
       </c>
       <c r="N31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>4793558.038174816</v>
+        <v>4789944.592232486</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0.8273931998866385</v>
+        <v>0.8267695002094817</v>
       </c>
     </row>
     <row r="32">
@@ -2184,25 +2184,25 @@
         <v>7374506.62</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.01972492788163938</v>
+        <v>0.0197962021949552</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1272889.990093001</v>
+        <v>1277489.467491086</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>6101616.629906999</v>
+        <v>6097017.152508914</v>
       </c>
       <c r="N32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>6101616.629906999</v>
+        <v>6097017.152508914</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0.8273931998866385</v>
+        <v>0.8267695002094817</v>
       </c>
     </row>
     <row r="33">
@@ -2230,10 +2230,10 @@
         <v>-17601329.94</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>49575811.2</v>
+        <v>48229737.91</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>373867355.27</v>
+        <v>372521281.98</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>1</v>
@@ -2245,16 +2245,16 @@
         <v>64532047.86</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>-30705264.01999997</v>
+        <v>-32051337.30999999</v>
       </c>
       <c r="N33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>-30705264.01999997</v>
+        <v>-32051337.30999999</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>-0.08212876461980799</v>
+        <v>-0.08603894290184678</v>
       </c>
     </row>
     <row r="34">
@@ -2290,25 +2290,25 @@
         <v>192570928.24</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.5239744982062241</v>
+        <v>0.5327493633766675</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>157982060.76</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>35194714.49191175</v>
+        <v>35784111.25728109</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>-605847.0119117349</v>
+        <v>-1195243.777281076</v>
       </c>
       <c r="N34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>-605847.0119117349</v>
+        <v>-1195243.777281076</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>-0.003146097998534189</v>
+        <v>-0.006206771646192879</v>
       </c>
     </row>
     <row r="35">
@@ -2344,25 +2344,25 @@
         <v>115579254.23</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.3144845501431949</v>
+        <v>0.3197511414279637</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>70217423.92</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>21123535.5772045</v>
+        <v>21477285.9548423</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>24238294.73279551</v>
+        <v>23884544.3551577</v>
       </c>
       <c r="N35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>24238294.73279551</v>
+        <v>23884544.3551577</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0.2097114650399272</v>
+        <v>0.2066507913922686</v>
       </c>
     </row>
     <row r="36">
@@ -2398,25 +2398,25 @@
         <v>24355117.2</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.06626888300459997</v>
+        <v>0.06737867081937333</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>5785422.41</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>4451198.340814775</v>
+        <v>4525741.406214455</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>14118496.44918522</v>
+        <v>14043953.38378554</v>
       </c>
       <c r="N36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>14118496.44918522</v>
+        <v>14043953.38378554</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.5796932255856779</v>
+        <v>0.5766325519380192</v>
       </c>
     </row>
     <row r="37">
@@ -2446,31 +2446,31 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>6053382.07</v>
+        <v>0</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>6053382.07</v>
+        <v>0</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.01647090690982071</v>
+        <v>0</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>6115790.4</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>1106330.304429901</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>-1168738.634429901</v>
+        <v>-6115790.4</v>
       </c>
       <c r="N37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>-1168738.634429901</v>
+        <v>-6115790.4</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>-0.1930720084929153</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2506,25 +2506,25 @@
         <v>15264311.37</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.0415333195080792</v>
+        <v>0.0422288672494521</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>1691430.78</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>2789741.346176898</v>
+        <v>2836460.421736714</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>10783139.2438231</v>
+        <v>10736420.16826329</v>
       </c>
       <c r="N38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>10783139.2438231</v>
+        <v>10736420.16826329</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>0.7064281501107182</v>
+        <v>0.7033674764630595</v>
       </c>
     </row>
     <row r="39">
@@ -2560,25 +2560,25 @@
         <v>6322158</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.01720223086582379</v>
+        <v>0.01749031216938951</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1155452.423771086</v>
+        <v>1174802.486158021</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>5166705.576228915</v>
+        <v>5147355.513841979</v>
       </c>
       <c r="N39" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>5166705.576228915</v>
+        <v>5147355.513841979</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>0.8172376546471813</v>
+        <v>0.8141769809995225</v>
       </c>
     </row>
     <row r="40">
@@ -2614,25 +2614,25 @@
         <v>7374506.62</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.02006561136225729</v>
+        <v>0.02040164495715379</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1347782.125691088</v>
+        <v>1370353.083767407</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>6026724.494308912</v>
+        <v>6004153.536232593</v>
       </c>
       <c r="N40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>6026724.494308912</v>
+        <v>6004153.536232593</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0.8172376546471812</v>
+        <v>0.8141769809995225</v>
       </c>
     </row>
     <row r="41">
@@ -2660,10 +2660,10 @@
         <v>-20863268.36</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>52804103.78</v>
+        <v>46750721.71</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>367519657.73</v>
+        <v>361466275.66</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>1</v>
@@ -2675,16 +2675,16 @@
         <v>67168754.61</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>58558774.85000001</v>
+        <v>52505392.78000002</v>
       </c>
       <c r="N41" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>58558774.85000001</v>
+        <v>52505392.78000002</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.1593350821332678</v>
+        <v>0.1452566845527445</v>
       </c>
     </row>
   </sheetData>

--- a/estado_resultado/TABLERO_Resumen.xlsx
+++ b/estado_resultado/TABLERO_Resumen.xlsx
@@ -570,25 +570,25 @@
         <v>203938603.8</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.5302666766389033</v>
+        <v>0.531305845820203</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>180204999.95</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>26342638.17832172</v>
+        <v>26394262.12331964</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>-2609034.328321721</v>
+        <v>-2660658.27331965</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>-2609034.328321721</v>
+        <v>-2660658.27331965</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>-0.01279323423671356</v>
+        <v>-0.01304636897450237</v>
       </c>
     </row>
     <row r="3">
@@ -624,25 +624,25 @@
         <v>129557254</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.3368655724465751</v>
+        <v>0.3375257314506185</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>62112578.1</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>16734839.80917067</v>
+        <v>16767635.25069059</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>50709836.09082934</v>
+        <v>50677040.64930941</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>50709836.09082934</v>
+        <v>50677040.64930941</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.3914086978937462</v>
+        <v>0.3911555631559574</v>
       </c>
     </row>
     <row r="4">
@@ -678,25 +678,25 @@
         <v>19765790.76</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.0513936056349776</v>
+        <v>0.0514943222242799</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>13033700.32</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>2553136.407708871</v>
+        <v>2558139.815970092</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>4178954.03229113</v>
+        <v>4173950.62402991</v>
       </c>
       <c r="N4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>4178954.03229113</v>
+        <v>4173950.62402991</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.2114235692886152</v>
+        <v>0.2111704345508264</v>
       </c>
     </row>
     <row r="5">
@@ -726,31 +726,31 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>5339979</v>
+        <v>4587755.72</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>5339979</v>
+        <v>4587755.72</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.01388463422270195</v>
+        <v>0.01195213357261924</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>940255.37</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>689762.1737902485</v>
+        <v>593759.2234876282</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3709961.456209751</v>
+        <v>3053741.126512371</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>3709961.456209751</v>
+        <v>3053741.126512371</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.6947520685399233</v>
+        <v>0.6656285366720379</v>
       </c>
     </row>
     <row r="6">
@@ -786,25 +786,25 @@
         <v>13187022.16</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.03428795865644135</v>
+        <v>0.03435515312951535</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>1670327.5</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1703360.457204378</v>
+        <v>1706698.550601065</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>9813334.202795623</v>
+        <v>9809996.109398935</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>9813334.202795623</v>
+        <v>9809996.109398935</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0.7441660508133721</v>
+        <v>0.7439129160755831</v>
       </c>
     </row>
     <row r="7">
@@ -840,25 +840,25 @@
         <v>5784313.96</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.01503996243503367</v>
+        <v>0.01506943640754398</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>747156.6781320452</v>
+        <v>748620.8889295979</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5037157.281867955</v>
+        <v>5035693.071070402</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>5037157.281867955</v>
+        <v>5035693.071070402</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.8708305456275673</v>
+        <v>0.8705774108897786</v>
       </c>
     </row>
     <row r="8">
@@ -894,25 +894,25 @@
         <v>7023340</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.01826158996536719</v>
+        <v>0.01829737739522008</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>907200.995672081</v>
+        <v>908978.8470013826</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6116139.004327919</v>
+        <v>6114361.152998617</v>
       </c>
       <c r="N8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>6116139.004327919</v>
+        <v>6114361.152998617</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.8708305456275675</v>
+        <v>0.8705774108897785</v>
       </c>
     </row>
     <row r="9">
@@ -940,10 +940,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>40041270.36</v>
+        <v>39289047.08</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>384596303.6799999</v>
+        <v>383844080.4</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>1</v>
@@ -955,16 +955,16 @@
         <v>49678094.7</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>76904395.49999996</v>
+        <v>76152172.21999998</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>76904395.49999996</v>
+        <v>76152172.21999998</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>0.1999613484688808</v>
+        <v>0.1983935043120701</v>
       </c>
     </row>
     <row r="10">

--- a/estado_resultado/TABLERO_Resumen.xlsx
+++ b/estado_resultado/TABLERO_Resumen.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:P49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2293,22 +2293,22 @@
         <v>0.5327493633766675</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>149363408.98</v>
+        <v>153054155.65</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>35784111.25728109</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>7423408.002718925</v>
+        <v>3732661.332718909</v>
       </c>
       <c r="N34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>7423408.002718925</v>
+        <v>3732661.332718909</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0.03854895476988705</v>
+        <v>0.01938330653974371</v>
       </c>
     </row>
     <row r="35">
@@ -2669,22 +2669,452 @@
         <v>1</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>257979587.07</v>
+        <v>261670333.74</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>67168754.61</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>36317933.98000003</v>
+        <v>32627187.31000002</v>
       </c>
       <c r="N41" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>36317933.98000003</v>
+        <v>32627187.31000002</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.1004739208759856</v>
+        <v>0.09026343398267556</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Junio 2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>OSPEVIC</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>8981</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>22496.83</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>202044030.23</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>-16731419.21</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>197312611.02</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>0.5387993528609455</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>38699011.01092069</v>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>158613600.0090793</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>158613600.0090793</v>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>0.8038695509077316</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Junio 2026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>OSPIF</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>4174</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>23000</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>96002000</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>19577254.23</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>115579254.23</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>0.3156109843225504</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>22668611.03787937</v>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>92910643.19212063</v>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>92910643.19212063</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>0.8038695509077315</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Junio 2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>OSPLYFC</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>927</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>20087.6</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>18621205.2</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>5733912</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>24355117.2</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>0.06650624771714342</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>4776780.074130833</v>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>19578337.12586917</v>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v>19578337.12586917</v>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>0.8038695509077315</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Junio 2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>OSPM</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Junio 2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>OSSURRBAC</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>303</v>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>24823.17</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>7521420.51</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>7742890.86</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>15264311.37</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>0.04168208532393467</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>2993796.24408232</v>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>12270515.12591768</v>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="2" t="n">
+        <v>12270515.12591768</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>0.8038695509077315</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Junio 2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>AMSURRBAC</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>6322158</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>6322158</v>
+      </c>
+      <c r="J47" s="3" t="n">
+        <v>0.01726384655028143</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>1239967.687772278</v>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>5082190.312227722</v>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="2" t="n">
+        <v>5082190.312227722</v>
+      </c>
+      <c r="P47" s="3" t="n">
+        <v>0.8038695509077316</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Junio 2026</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>UOM</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>7374506.62</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>7374506.62</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>0.02013748322514473</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>1446365.295214507</v>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>5928141.324785493</v>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="2" t="n">
+        <v>5928141.324785493</v>
+      </c>
+      <c r="P48" s="3" t="n">
+        <v>0.8038695509077315</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Junio 2026</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>14385</v>
+      </c>
+      <c r="D49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="n">
+        <v>324188655.94</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>-16731419.21</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>46750721.71</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>366207958.44</v>
+      </c>
+      <c r="J49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>71824531.34999999</v>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>294383427.09</v>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="2" t="n">
+        <v>294383427.09</v>
+      </c>
+      <c r="P49" s="3" t="n">
+        <v>0.8038695509077316</v>
       </c>
     </row>
   </sheetData>
@@ -2698,7 +3128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3499,17 +3929,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Refacturacion</t>
+          <t>Intereses</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>2247965.94</v>
+        <v>3690746.67</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1316301.72</v>
+        <v>3690746.67</v>
       </c>
     </row>
     <row r="39">
@@ -3520,16 +3950,37 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>Refacturacion</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>19</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>2247965.94</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>1316301.72</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Mayo 2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>Traslado</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="C40" t="n">
         <v>2</v>
       </c>
-      <c r="D39" s="2" t="n">
+      <c r="D40" s="2" t="n">
         <v>206809.24</v>
       </c>
-      <c r="E39" s="2" t="n">
+      <c r="E40" s="2" t="n">
         <v>206809.24</v>
       </c>
     </row>
@@ -17924,10 +18375,10 @@
         </is>
       </c>
       <c r="C411" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D411" s="2" t="n">
-        <v>18625880.97</v>
+        <v>20966096.97</v>
       </c>
       <c r="E411" s="2" t="n">
         <v>19191.94</v>
@@ -17936,10 +18387,10 @@
         <v>1103687.18</v>
       </c>
       <c r="G411" s="3" t="n">
-        <v>0.0603</v>
+        <v>0.0536</v>
       </c>
       <c r="H411" s="2" t="n">
-        <v>17503001.85</v>
+        <v>19843217.85</v>
       </c>
       <c r="I411" t="inlineStr">
         <is>
@@ -18029,10 +18480,10 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D414" s="2" t="n">
-        <v>9233418.380000001</v>
+        <v>10196611.78</v>
       </c>
       <c r="E414" s="2" t="n">
         <v>544094.41</v>
@@ -18041,10 +18492,10 @@
         <v>289381.52</v>
       </c>
       <c r="G414" s="3" t="n">
-        <v>0.09029999999999999</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="H414" s="2" t="n">
-        <v>8399942.449999999</v>
+        <v>9363135.85</v>
       </c>
       <c r="I414" t="inlineStr">
         <is>
@@ -18165,30 +18616,30 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>SANATORIO DEL SALVADOR PRIVADO SA</t>
+          <t>COSEME SA</t>
         </is>
       </c>
       <c r="C418" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D418" s="2" t="n">
-        <v>8313507.54</v>
+        <v>7580494.76</v>
       </c>
       <c r="E418" s="2" t="n">
-        <v>1135773.62</v>
+        <v>0</v>
       </c>
       <c r="F418" s="2" t="n">
-        <v>0</v>
+        <v>362723.19</v>
       </c>
       <c r="G418" s="3" t="n">
-        <v>0.1366</v>
+        <v>0.0478</v>
       </c>
       <c r="H418" s="2" t="n">
-        <v>7177733.92</v>
+        <v>7217771.57</v>
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>OSPEVIC, OSPIF, OSPM</t>
+          <t>OSPEVIC</t>
         </is>
       </c>
     </row>
@@ -18200,30 +18651,30 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>COSEME SA</t>
+          <t>SANATORIO DEL SALVADOR PRIVADO SA</t>
         </is>
       </c>
       <c r="C419" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D419" s="2" t="n">
-        <v>7241278.34</v>
+        <v>8313507.54</v>
       </c>
       <c r="E419" s="2" t="n">
-        <v>0</v>
+        <v>1135773.62</v>
       </c>
       <c r="F419" s="2" t="n">
-        <v>362723.19</v>
+        <v>0</v>
       </c>
       <c r="G419" s="3" t="n">
-        <v>0.0501</v>
+        <v>0.1366</v>
       </c>
       <c r="H419" s="2" t="n">
-        <v>6878555.15</v>
+        <v>7177733.92</v>
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>OSPEVIC</t>
+          <t>OSPEVIC, OSPIF, OSPM</t>
         </is>
       </c>
     </row>
@@ -19145,14 +19596,14 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>EL JUNCO SERVICIOS SOCIALES SA</t>
+          <t>DE LA VILLA SERVICIOS ASISTENCIALES S.A.</t>
         </is>
       </c>
       <c r="C446" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D446" s="2" t="n">
-        <v>825293</v>
+        <v>830896.4399999999</v>
       </c>
       <c r="E446" s="2" t="n">
         <v>0</v>
@@ -19164,7 +19615,7 @@
         <v>0</v>
       </c>
       <c r="H446" s="2" t="n">
-        <v>825293</v>
+        <v>830896.4399999999</v>
       </c>
       <c r="I446" t="inlineStr">
         <is>
@@ -19180,14 +19631,14 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>DE LA VILLA SERVICIOS ASISTENCIALES S.A.</t>
+          <t>EL JUNCO SERVICIOS SOCIALES SA</t>
         </is>
       </c>
       <c r="C447" t="n">
         <v>4</v>
       </c>
       <c r="D447" s="2" t="n">
-        <v>782775.59</v>
+        <v>825293</v>
       </c>
       <c r="E447" s="2" t="n">
         <v>0</v>
@@ -19199,11 +19650,11 @@
         <v>0</v>
       </c>
       <c r="H447" s="2" t="n">
-        <v>782775.59</v>
+        <v>825293</v>
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>OSPIF, OSPLYFC, OSSURRBAC</t>
+          <t>OSPEVIC, OSPIF, OSPLYFC, OSSURRBAC</t>
         </is>
       </c>
     </row>
@@ -21598,7 +22049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1389"/>
+  <dimension ref="A1:L1393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -89748,6 +90199,214 @@
         <v>1899144.75</v>
       </c>
     </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>Mayo 2026</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE BENEFICENCIA HOSPITAL ITALIANO</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>00024-00000607</t>
+        </is>
+      </c>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E1390" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="F1390" t="inlineStr">
+        <is>
+          <t>Intereses</t>
+        </is>
+      </c>
+      <c r="G1390" t="inlineStr">
+        <is>
+          <t>OSPEVIC</t>
+        </is>
+      </c>
+      <c r="H1390" t="n">
+        <v>88</v>
+      </c>
+      <c r="I1390" s="2" t="n">
+        <v>2340216</v>
+      </c>
+      <c r="J1390" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1390" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1390" s="2" t="n">
+        <v>2340216</v>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>Mayo 2026</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>COSEME SA</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>00046-00000227</t>
+        </is>
+      </c>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E1391" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="F1391" t="inlineStr">
+        <is>
+          <t>Intereses</t>
+        </is>
+      </c>
+      <c r="G1391" t="inlineStr">
+        <is>
+          <t>OSPEVIC</t>
+        </is>
+      </c>
+      <c r="H1391" t="n">
+        <v>87</v>
+      </c>
+      <c r="I1391" s="2" t="n">
+        <v>339216.42</v>
+      </c>
+      <c r="J1391" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1391" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1391" s="2" t="n">
+        <v>339216.42</v>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>Mayo 2026</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>CIPREM SRL</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>00004-00015036</t>
+        </is>
+      </c>
+      <c r="D1392" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E1392" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="F1392" t="inlineStr">
+        <is>
+          <t>Intereses</t>
+        </is>
+      </c>
+      <c r="G1392" t="inlineStr">
+        <is>
+          <t>OSPEVIC</t>
+        </is>
+      </c>
+      <c r="H1392" t="n">
+        <v>88</v>
+      </c>
+      <c r="I1392" s="2" t="n">
+        <v>963193.4</v>
+      </c>
+      <c r="J1392" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1392" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1392" s="2" t="n">
+        <v>963193.4</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>Mayo 2026</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>DE LA VILLA SERVICIOS ASISTENCIALES S.A.</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>00004-00000428</t>
+        </is>
+      </c>
+      <c r="D1393" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E1393" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="F1393" t="inlineStr">
+        <is>
+          <t>Intereses</t>
+        </is>
+      </c>
+      <c r="G1393" t="inlineStr">
+        <is>
+          <t>OSPEVIC</t>
+        </is>
+      </c>
+      <c r="H1393" t="n">
+        <v>88</v>
+      </c>
+      <c r="I1393" s="2" t="n">
+        <v>48120.85</v>
+      </c>
+      <c r="J1393" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1393" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1393" s="2" t="n">
+        <v>48120.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -89759,7 +90418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -89891,6 +90550,25 @@
         <v>0</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Junio 2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estado_resultado/TABLERO_Resumen.xlsx
+++ b/estado_resultado/TABLERO_Resumen.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P49"/>
+  <dimension ref="A1:P57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -444,7 +444,7 @@
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
@@ -570,25 +570,25 @@
         <v>228484756.64</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.5496976741009947</v>
+        <v>0.5510825208873709</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>180204999.95</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>27307933.11035895</v>
+        <v>27376729.66015754</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>20971823.57964104</v>
+        <v>20903027.02984246</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0</v>
+        <v>7564252.635759039</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>20971823.57964104</v>
+        <v>13338774.39408342</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0.09178653266871627</v>
+        <v>0.05837927479381025</v>
       </c>
     </row>
     <row r="3">
@@ -621,28 +621,28 @@
         <v>14557254</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>136822329.86</v>
+        <v>135777805.86</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.329172578491191</v>
+        <v>0.3274825709785908</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>62112578.1</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>16352666.52692857</v>
+        <v>16268710.17367391</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>58357085.23307145</v>
+        <v>57396517.58632611</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0</v>
+        <v>4495081.601755664</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>58357085.23307145</v>
+        <v>52901435.98457044</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.4265172599588375</v>
+        <v>0.3896176967178047</v>
       </c>
     </row>
     <row r="4">
@@ -678,25 +678,25 @@
         <v>19765790.76</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.04755332201289091</v>
+        <v>0.04767312252919974</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>13033700.32</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>2362358.434255989</v>
+        <v>2368309.895650289</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>4369732.005744012</v>
+        <v>4363780.544349713</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0</v>
+        <v>654369.4076264558</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>4369732.005744012</v>
+        <v>3709411.136723258</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.2210754964879539</v>
+        <v>0.1876682386130479</v>
       </c>
     </row>
     <row r="5">
@@ -732,25 +732,25 @@
         <v>4587755.72</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.01103740435779267</v>
+        <v>0.01106521075879268</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>940255.37</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>548317.2189286171</v>
+        <v>549698.5879507617</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3099183.131071383</v>
+        <v>3097801.762049238</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0</v>
+        <v>151882.9693829706</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>3099183.131071383</v>
+        <v>2945918.792666268</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.6755335986091654</v>
+        <v>0.6421263407342594</v>
       </c>
     </row>
     <row r="6">
@@ -786,25 +786,25 @@
         <v>13187022.16</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.031725860036657</v>
+        <v>0.03180578661700617</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>1670327.5</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1576080.279339992</v>
+        <v>1580050.879567625</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>9940614.380660009</v>
+        <v>9936643.780432375</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0</v>
+        <v>436571.6496735871</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>9940614.380660009</v>
+        <v>9500072.130758788</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0.7538179780127107</v>
+        <v>0.7204107201378047</v>
       </c>
     </row>
     <row r="7">
@@ -840,25 +840,25 @@
         <v>5784313.96</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.01391613154785517</v>
+        <v>0.01395119029188997</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>691326.9008920066</v>
+        <v>693068.5524982308</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5092987.059107994</v>
+        <v>5091245.407501769</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0</v>
+        <v>191496.4164849147</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>5092987.059107994</v>
+        <v>4899748.991016855</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.8804824728269062</v>
+        <v>0.847075214952</v>
       </c>
     </row>
     <row r="8">
@@ -894,25 +894,25 @@
         <v>7023340</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.01689702945261863</v>
+        <v>0.01693959793714975</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>839412.2292958775</v>
+        <v>841526.9505016502</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6183927.770704122</v>
+        <v>6181813.049498349</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0</v>
+        <v>232515.8093173698</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>6183927.770704122</v>
+        <v>5949297.240180979</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.8804824728269061</v>
+        <v>0.847075214952</v>
       </c>
     </row>
     <row r="9">
@@ -943,7 +943,7 @@
         <v>39289047.08</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>415655309.1</v>
+        <v>414610785.1</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>1</v>
@@ -955,16 +955,16 @@
         <v>49678094.7</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>107963400.92</v>
+        <v>106918876.92</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0</v>
+        <v>13726170.49</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>107963400.92</v>
+        <v>93192706.42999998</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>0.2597426246130919</v>
+        <v>0.2247715442508878</v>
       </c>
     </row>
     <row r="10">
@@ -1012,13 +1012,13 @@
         <v>-29195163.61312122</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>223833.6568357974</v>
+        <v>286825.4897875541</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>-29418997.26995701</v>
+        <v>-29481989.10290877</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>-0.1365787768588533</v>
+        <v>-0.1368712187601764</v>
       </c>
     </row>
     <row r="11">
@@ -1066,13 +1066,13 @@
         <v>78223657.08636367</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>157948.6792438911</v>
+        <v>202398.9954230198</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>78065708.40711978</v>
+        <v>78021258.09094065</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.5136000406098303</v>
+        <v>0.5133075987085072</v>
       </c>
     </row>
     <row r="12">
@@ -1120,13 +1120,13 @@
         <v>13729119.55711576</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>33165.32260993544</v>
+        <v>42498.79145090046</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>13695954.23450582</v>
+        <v>13686620.76566486</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.4291299371135243</v>
+        <v>0.428837495212201</v>
       </c>
     </row>
     <row r="13">
@@ -1174,13 +1174,13 @@
         <v>2905696.382826977</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>5549.071134847688</v>
+        <v>7110.704746633625</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>2900147.31169213</v>
+        <v>2898585.678080344</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.54310088329788</v>
+        <v>0.5428084413965567</v>
       </c>
     </row>
     <row r="14">
@@ -1228,13 +1228,13 @@
         <v>5413877.925705466</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>18017.36991584499</v>
+        <v>23087.86365665673</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>5395860.555789622</v>
+        <v>5390790.06204881</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.3112075077637968</v>
+        <v>0.3109150658624736</v>
       </c>
     </row>
     <row r="15">
@@ -1282,13 +1282,13 @@
         <v>5021410.775529231</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>6010.804467645384</v>
+        <v>7702.380239958087</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>5015399.971061585</v>
+        <v>5013708.395289273</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>0.8670691123864213</v>
+        <v>0.8667766704850981</v>
       </c>
     </row>
     <row r="16">
@@ -1336,13 +1336,13 @@
         <v>6097019.525580086</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>7298.345792037977</v>
+        <v>9352.26469527723</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>6089721.179788047</v>
+        <v>6087667.260884808</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.8670691123864211</v>
+        <v>0.866776670485098</v>
       </c>
     </row>
     <row r="17">
@@ -1388,13 +1388,13 @@
         <v>82195617.63999999</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>451823.25</v>
+        <v>578976.49</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>81743794.38999999</v>
+        <v>81616641.14999999</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.1880039443177695</v>
+        <v>0.1877115024164463</v>
       </c>
     </row>
     <row r="18">
@@ -1442,13 +1442,13 @@
         <v>-16982166.59964171</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0</v>
+        <v>168011.5449564625</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>-16982166.59964171</v>
+        <v>-17150178.14459818</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>-0.09236056785106175</v>
+        <v>-0.09327432886068703</v>
       </c>
     </row>
     <row r="19">
@@ -1496,13 +1496,13 @@
         <v>11456956.02895906</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0</v>
+        <v>161777.3418539799</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>11456956.02895906</v>
+        <v>11295178.68710508</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>0.06471190333750899</v>
+        <v>0.06379814232788374</v>
       </c>
     </row>
     <row r="20">
@@ -1550,13 +1550,13 @@
         <v>5750130.929361717</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0</v>
+        <v>18626.67837176676</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>5750130.929361717</v>
+        <v>5731504.25098995</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.2820817184160491</v>
+        <v>0.2811679574064239</v>
       </c>
     </row>
     <row r="21">
@@ -1604,13 +1604,13 @@
         <v>-2099270.738894804</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0</v>
+        <v>5531.344511930675</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>-2099270.738894804</v>
+        <v>-2104802.083406735</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-0.3467930348058807</v>
+        <v>-0.347706795815506</v>
       </c>
     </row>
     <row r="22">
@@ -1658,13 +1658,13 @@
         <v>7009902.510231229</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0</v>
+        <v>12413.28985873526</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>7009902.510231229</v>
+        <v>6997489.220372493</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0.5160095081978679</v>
+        <v>0.5150957471882427</v>
       </c>
     </row>
     <row r="23">
@@ -1712,13 +1712,13 @@
         <v>4959044.862143656</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0</v>
+        <v>5293.935740902937</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>4959044.862143656</v>
+        <v>4953750.926402753</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.8559570916205518</v>
+        <v>0.8550433306109265</v>
       </c>
     </row>
     <row r="24">
@@ -1766,13 +1766,13 @@
         <v>6011678.107840832</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0</v>
+        <v>6417.654706222012</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>6011678.107840832</v>
+        <v>6005260.45313461</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>0.8559570916205518</v>
+        <v>0.8550433306109265</v>
       </c>
     </row>
     <row r="25">
@@ -1818,13 +1818,13 @@
         <v>9854351.920000039</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0</v>
+        <v>378071.79</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>9854351.920000039</v>
+        <v>9476280.13000004</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>0.02381696491986853</v>
+        <v>0.02290320391024327</v>
       </c>
     </row>
     <row r="26">
@@ -1860,25 +1860,25 @@
         <v>193070963.46</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.5177683860026663</v>
+        <v>0.5055118775576929</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>180713484.99</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>33412654.26591901</v>
+        <v>32621716.6763515</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-21055175.79591902</v>
+        <v>-20264238.2063515</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0</v>
+        <v>195258.0017465606</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>-21055175.79591902</v>
+        <v>-20459496.20809806</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-0.109054077415847</v>
+        <v>-0.1059687890993345</v>
       </c>
     </row>
     <row r="27">
@@ -1914,25 +1914,25 @@
         <v>125864669.28</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.337537791804548</v>
+        <v>0.3295476655094891</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>108657862.98</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>21782004.93528981</v>
+        <v>21266385.72280962</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>-4575198.635289811</v>
+        <v>-4059579.422809627</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0</v>
+        <v>127290.4188888876</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>-4575198.635289811</v>
+        <v>-4186869.841698514</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.03635014227155176</v>
+        <v>-0.03326485395503924</v>
       </c>
     </row>
     <row r="28">
@@ -1965,28 +1965,28 @@
         <v>1973112</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>20442924.55</v>
+        <v>22669682.24</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.05482284782621234</v>
+        <v>0.05935534493333017</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>7808659.21</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>3537830.639742632</v>
+        <v>3830321.959984471</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>9096434.700257368</v>
+        <v>11030701.07001553</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0</v>
+        <v>22926.4762297048</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>9096434.700257368</v>
+        <v>11007774.59378583</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.4449673860512961</v>
+        <v>0.485572513864483</v>
       </c>
     </row>
     <row r="29">
@@ -2022,25 +2022,25 @@
         <v>4707308.78</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.01262383336032678</v>
+        <v>0.01232500453189385</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>1117878.5</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>814641.8185852723</v>
+        <v>795357.7823268911</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2774788.461414728</v>
+        <v>2794072.497673109</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0</v>
+        <v>4760.631477230211</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>2774788.461414728</v>
+        <v>2789311.866195879</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.5894638722668896</v>
+        <v>0.5925491605834021</v>
       </c>
     </row>
     <row r="30">
@@ -2076,25 +2076,25 @@
         <v>15636658.92</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.04193363676439073</v>
+        <v>0.04094099220163723</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>3274750.16</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>2706063.454623518</v>
+        <v>2642006.06819194</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>9655845.305376481</v>
+        <v>9719902.69180806</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0</v>
+        <v>15813.78535641007</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>9655845.305376481</v>
+        <v>9704088.90645165</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>0.6175133290799235</v>
+        <v>0.6205986173964361</v>
       </c>
     </row>
     <row r="31">
@@ -2130,25 +2130,25 @@
         <v>5793567.12</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.01553690851883065</v>
+        <v>0.01516912196480793</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>1002628.524133621</v>
+        <v>978894.5046271626</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>4790938.595866378</v>
+        <v>4814672.615372838</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0</v>
+        <v>5859.194560191562</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>4790938.595866378</v>
+        <v>4808813.420812646</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0.826941070437858</v>
+        <v>0.8300263587543706</v>
       </c>
     </row>
     <row r="32">
@@ -2184,25 +2184,25 @@
         <v>7374506.62</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.01977659572302513</v>
+        <v>0.01930844815155322</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1276224.221706129</v>
+        <v>1246013.700218361</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>6098282.398293871</v>
+        <v>6128492.919781639</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0</v>
+        <v>7458.042373038161</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>6098282.398293871</v>
+        <v>6121034.877408601</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0.8269410704378581</v>
+        <v>0.8300263587543707</v>
       </c>
     </row>
     <row r="33">
@@ -2233,7 +2233,7 @@
         <v>48229737.91</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>372890598.73</v>
+        <v>381931606.42</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>1</v>
@@ -2245,16 +2245,16 @@
         <v>64532047.86</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>444404.6600000411</v>
+        <v>9485412.350000039</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0</v>
+        <v>386257.99</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>444404.6600000411</v>
+        <v>9099154.360000039</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>0.001191782955949025</v>
+        <v>0.02382404128658035</v>
       </c>
     </row>
     <row r="34">
@@ -2290,25 +2290,25 @@
         <v>192570928.24</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.5327493633766675</v>
+        <v>0.5087581768263865</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>153054155.65</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>35784111.25728109</v>
+        <v>34172653.13508254</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3732661.332718909</v>
+        <v>5344119.454917461</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0</v>
+        <v>488789.9220565459</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>3732661.332718909</v>
+        <v>4855329.532860915</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0.01938330653974371</v>
+        <v>0.02521320106433587</v>
       </c>
     </row>
     <row r="35">
@@ -2341,28 +2341,28 @@
         <v>19577254.23</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>115579254.23</v>
+        <v>129048579.65</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.3197511414279637</v>
+        <v>0.340936821070644</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>91886204.93000001</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>21477285.9548423</v>
+        <v>22900301.67200757</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2215763.345157698</v>
+        <v>11426231.73799243</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0</v>
+        <v>327555.3883710741</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>2215763.345157698</v>
+        <v>11098676.34962136</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0.01917094343547485</v>
+        <v>0.08600386288421544</v>
       </c>
     </row>
     <row r="36">
@@ -2395,28 +2395,28 @@
         <v>5733912</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>24355117.2</v>
+        <v>27931227.6</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.06737867081937333</v>
+        <v>0.07379224143630188</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>7418153.95</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>4525741.406214455</v>
+        <v>4956532.957156835</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>12411221.84378554</v>
+        <v>15556540.69284316</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0</v>
+        <v>70895.96901424605</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>12411221.84378554</v>
+        <v>15485644.72382892</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.5095940102388645</v>
+        <v>0.5544204839685929</v>
       </c>
     </row>
     <row r="37">
@@ -2506,25 +2506,25 @@
         <v>15264311.37</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.0422288672494521</v>
+        <v>0.04032718382825136</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>1584662.11</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>2836460.421736714</v>
+        <v>2708726.714672176</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>10843188.83826329</v>
+        <v>10970922.54532783</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0</v>
+        <v>38744.38178690448</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>10843188.83826329</v>
+        <v>10932178.16354092</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>0.710362136583125</v>
+        <v>0.7161920311077171</v>
       </c>
     </row>
     <row r="39">
@@ -2560,25 +2560,25 @@
         <v>6322158</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.01749031216938951</v>
+        <v>0.01670267473436962</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1174802.486158021</v>
+        <v>1121897.86056352</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>5147355.513841979</v>
+        <v>5200260.13943648</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0</v>
+        <v>16047.1112866936</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>5147355.513841979</v>
+        <v>5184213.028149786</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>0.8141769809995225</v>
+        <v>0.8200068755241148</v>
       </c>
     </row>
     <row r="40">
@@ -2614,25 +2614,25 @@
         <v>7374506.62</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.02040164495715379</v>
+        <v>0.01948290210404667</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1370353.083767407</v>
+        <v>1308642.270517364</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>6004153.536232593</v>
+        <v>6065864.349482637</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0</v>
+        <v>18718.21748453593</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>6004153.536232593</v>
+        <v>6047146.131998101</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0.8141769809995225</v>
+        <v>0.8200068755241149</v>
       </c>
     </row>
     <row r="41">
@@ -2663,7 +2663,7 @@
         <v>46750721.71</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>361466275.66</v>
+        <v>378511711.48</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>1</v>
@@ -2675,16 +2675,16 @@
         <v>67168754.61</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>32627187.31000002</v>
+        <v>46836781.82000001</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0</v>
+        <v>960750.99</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>32627187.31000002</v>
+        <v>45876030.83000001</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.09026343398267556</v>
+        <v>0.1212010868847952</v>
       </c>
     </row>
     <row r="42">
@@ -2720,25 +2720,25 @@
         <v>197312611.02</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.5387993528609455</v>
+        <v>0.4708070268433051</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>38699011.01092069</v>
+        <v>43397074.29276185</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>158613600.0090793</v>
+        <v>153915536.7272382</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0</v>
+        <v>946812.6389640301</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>158613600.0090793</v>
+        <v>152968724.0882742</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>0.8038695509077316</v>
+        <v>0.7752607565097241</v>
       </c>
     </row>
     <row r="43">
@@ -2753,13 +2753,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4174</v>
+        <v>4086</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>23000</v>
+        <v>26507</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>96002000</v>
+        <v>108307602</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>0</v>
@@ -2768,31 +2768,31 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>19577254.23</v>
+        <v>14577254.16</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>115579254.23</v>
+        <v>122884856.16</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.3156109843225504</v>
+        <v>0.2932151851504945</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>22668611.03787937</v>
+        <v>27027381.59848448</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>92910643.19212063</v>
+        <v>81680243.65151553</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0</v>
+        <v>589668.0113252947</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>92910643.19212063</v>
+        <v>81090575.64019023</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>0.8038695509077315</v>
+        <v>0.6598907153751128</v>
       </c>
     </row>
     <row r="44">
@@ -2807,13 +2807,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>927</v>
+        <v>916</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>20087.6</v>
+        <v>21770.94</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>18621205.2</v>
+        <v>19942181.04</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>0</v>
@@ -2822,31 +2822,31 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>5733912</v>
+        <v>9450166.880000001</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>24355117.2</v>
+        <v>58122623.34</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.06650624771714342</v>
+        <v>0.138686216484485</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>4776780.074130833</v>
+        <v>12783530.61234653</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>19578337.12586917</v>
+        <v>45339092.72765347</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0</v>
+        <v>278903.7867553213</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>19578337.12586917</v>
+        <v>45060188.94089815</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>0.8038695509077315</v>
+        <v>0.7752607565097241</v>
       </c>
     </row>
     <row r="45">
@@ -2876,31 +2876,31 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>0</v>
+        <v>11845329.66</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
+        <v>11845329.66</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0</v>
+        <v>0.02826410542323691</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0</v>
+        <v>2605270.127539745</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>0</v>
+        <v>9240059.532460256</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0</v>
+        <v>56840.29914158244</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>0</v>
+        <v>9183219.233318673</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>0</v>
+        <v>0.7752607565097241</v>
       </c>
     </row>
     <row r="46">
@@ -2915,13 +2915,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D46" s="2" t="n">
         <v>24823.17</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>7521420.51</v>
+        <v>7322835.149999999</v>
       </c>
       <c r="F46" s="2" t="n">
         <v>0</v>
@@ -2933,28 +2933,28 @@
         <v>7742890.86</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>15264311.37</v>
+        <v>15065726.01</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.04168208532393467</v>
+        <v>0.03594828345404127</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>2993796.24408232</v>
+        <v>3313566.36329795</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>12270515.12591768</v>
+        <v>11752159.64670205</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0</v>
+        <v>72293.50282122238</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>12270515.12591768</v>
+        <v>11679866.14388083</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>0.8038695509077315</v>
+        <v>0.7752607565097241</v>
       </c>
     </row>
     <row r="47">
@@ -2984,31 +2984,31 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>6322158</v>
+        <v>6488795.17</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>6322158</v>
+        <v>6488795.17</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.01726384655028143</v>
+        <v>0.01548289461069085</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>1239967.687772278</v>
+        <v>1427150.168493088</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>5082190.312227722</v>
+        <v>5061645.001506912</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0</v>
+        <v>31136.7491760677</v>
       </c>
       <c r="O47" s="2" t="n">
-        <v>5082190.312227722</v>
+        <v>5030508.252330844</v>
       </c>
       <c r="P47" s="3" t="n">
-        <v>0.8038695509077316</v>
+        <v>0.7752607565097241</v>
       </c>
     </row>
     <row r="48">
@@ -3044,25 +3044,25 @@
         <v>7374506.62</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.02013748322514473</v>
+        <v>0.01759628803374633</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>1446365.295214507</v>
+        <v>1621954.167076351</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>5928141.324785493</v>
+        <v>5752552.45292365</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0</v>
+        <v>35386.87181648097</v>
       </c>
       <c r="O48" s="2" t="n">
-        <v>5928141.324785493</v>
+        <v>5717165.581107169</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.8038695509077315</v>
+        <v>0.7752607565097243</v>
       </c>
     </row>
     <row r="49">
@@ -3077,11 +3077,11 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>14385</v>
+        <v>14278</v>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="2" t="n">
-        <v>324188655.94</v>
+        <v>337616648.42</v>
       </c>
       <c r="F49" s="2" t="n">
         <v>12000000</v>
@@ -3090,10 +3090,10 @@
         <v>-16731419.21</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>46750721.71</v>
+        <v>57478943.35</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>366207958.44</v>
+        <v>419094447.9800001</v>
       </c>
       <c r="J49" s="3" t="n">
         <v>1</v>
@@ -3102,19 +3102,449 @@
         <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>71824531.34999999</v>
+        <v>92175927.33</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>294383427.09</v>
+        <v>312741289.7400001</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0</v>
+        <v>2011041.86</v>
       </c>
       <c r="O49" s="2" t="n">
-        <v>294383427.09</v>
+        <v>310730247.8800001</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>0.8038695509077316</v>
+        <v>0.7414325085376188</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Julio 2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>OSPEVIC</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>8798</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>22688.05</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>199609463.9</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>-33144984.39</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>178464479.51</v>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>0.4898750349809923</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>43721092.66610041</v>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>134743386.8438996</v>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>1379308.255583632</v>
+      </c>
+      <c r="O50" s="2" t="n">
+        <v>133364078.5883159</v>
+      </c>
+      <c r="P50" s="3" t="n">
+        <v>0.7472864009380819</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Julio 2026</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>OSPIF</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>3960</v>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>26507</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>104967720</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>14577254.16</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>120062474.16</v>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>0.3295647900944839</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>29413486.49817181</v>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>83753716.29182819</v>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>927933.4590803272</v>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v>82825782.83274786</v>
+      </c>
+      <c r="P51" s="3" t="n">
+        <v>0.6898557056418058</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Julio 2026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>OSPLYFC</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>912</v>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>22329.38</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>20364394.56</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>5516125.68</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>25880520.24</v>
+      </c>
+      <c r="J52" s="3" t="n">
+        <v>0.07104058349709794</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>6340335.212736403</v>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>19540185.0272636</v>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>200024.2027088143</v>
+      </c>
+      <c r="O52" s="2" t="n">
+        <v>19340160.82455479</v>
+      </c>
+      <c r="P52" s="3" t="n">
+        <v>0.747286400938082</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Julio 2026</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>OSPM</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>10829115.38</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>10829115.38</v>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>0.02972531727409346</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>2652969.141651202</v>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>8176146.238348799</v>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v>83695.58068536952</v>
+      </c>
+      <c r="O53" s="2" t="n">
+        <v>8092450.657663429</v>
+      </c>
+      <c r="P53" s="3" t="n">
+        <v>0.7472864009380819</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Julio 2026</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>OSSURRBAC</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>286</v>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>24823.17</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>7099426.619999999</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>8106815.02</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>15206241.64</v>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>0.04174028454164751</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>3725298.735473586</v>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>11480942.90452641</v>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>117525.3175760184</v>
+      </c>
+      <c r="O54" s="2" t="n">
+        <v>11363417.58695039</v>
+      </c>
+      <c r="P54" s="3" t="n">
+        <v>0.7472864009380817</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Julio 2026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>AMSURRBAC</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>6488795.17</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>6488795.17</v>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>0.01781138055940219</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>1589656.472245045</v>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>4899138.697754955</v>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>50150.30874124559</v>
+      </c>
+      <c r="O55" s="2" t="n">
+        <v>4848988.38901371</v>
+      </c>
+      <c r="P55" s="3" t="n">
+        <v>0.747286400938082</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Julio 2026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>UOM</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>7374506.62</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>7374506.62</v>
+      </c>
+      <c r="J56" s="3" t="n">
+        <v>0.02024260905228277</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>1806642.353621548</v>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>5567864.266378452</v>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>56995.755624593</v>
+      </c>
+      <c r="O56" s="2" t="n">
+        <v>5510868.510753859</v>
+      </c>
+      <c r="P56" s="3" t="n">
+        <v>0.7472864009380819</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Julio 2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>13956</v>
+      </c>
+      <c r="D57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="n">
+        <v>332041005.08</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>-33144984.39</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>52892612.02999999</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>364306132.72</v>
+      </c>
+      <c r="J57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>89249481.08</v>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>268161380.27</v>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v>2815632.88</v>
+      </c>
+      <c r="O57" s="2" t="n">
+        <v>265345747.39</v>
+      </c>
+      <c r="P57" s="3" t="n">
+        <v>0.7283592658977844</v>
       </c>
     </row>
   </sheetData>
@@ -90418,14 +90848,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -90462,16 +90892,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0</v>
+        <v>12254444.49</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>1471726</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>13726170.49</v>
       </c>
     </row>
     <row r="3">
@@ -90487,10 +90917,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>127153.24</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>451823.25</v>
+        <v>578976.49</v>
       </c>
     </row>
     <row r="4">
@@ -90506,10 +90936,10 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>378071.79</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>378071.79</v>
       </c>
     </row>
     <row r="5">
@@ -90525,10 +90955,10 @@
         <v>0</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>386257.99</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>386257.99</v>
       </c>
     </row>
     <row r="6">
@@ -90544,10 +90974,10 @@
         <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>960750.99</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>960750.99</v>
       </c>
     </row>
     <row r="7">
@@ -90557,16 +90987,35 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0</v>
+        <v>828613.8199999999</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>1182428.04</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>2011041.86</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Julio 2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>2135105.8</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>680527.08</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>2815632.88</v>
       </c>
     </row>
   </sheetData>
